--- a/Exp3_PTO_GRPO/eda/results/arms/heterogeneity/tables/gpt-4o-mini/heterogeneity.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/heterogeneity/tables/gpt-4o-mini/heterogeneity.xlsx
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -760,19 +760,19 @@
         <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>4.796875</v>
+        <v>4.854044117647059</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1036124427157423</v>
+        <v>0.07414260445445435</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01831626521490102</v>
+        <v>0.01310668459614415</v>
       </c>
       <c r="J8" t="n">
         <v>4.371875</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4249999999999998</v>
+        <v>0.4821691176470591</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -803,19 +803,19 @@
         <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>3.037867647058824</v>
+        <v>3.408639705882353</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7686381709194494</v>
+        <v>0.7172720959879871</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1358773157339918</v>
+        <v>0.1267969907572485</v>
       </c>
       <c r="J9" t="n">
         <v>1.887683823529412</v>
       </c>
       <c r="K9" t="n">
-        <v>1.150183823529412</v>
+        <v>1.520955882352942</v>
       </c>
     </row>
     <row r="10">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -846,19 +846,19 @@
         <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>4.289889705882353</v>
+        <v>4.424264705882353</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1908045389500418</v>
+        <v>0.2445465015192218</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03372979584318683</v>
+        <v>0.04323012238492201</v>
       </c>
       <c r="J10" t="n">
         <v>2.629963235294118</v>
       </c>
       <c r="K10" t="n">
-        <v>1.659926470588236</v>
+        <v>1.794301470588235</v>
       </c>
     </row>
     <row r="11">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -889,19 +889,19 @@
         <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>4.752389705882353</v>
+        <v>4.854044117647059</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09864988103849653</v>
+        <v>0.07414260445445435</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01743899996139178</v>
+        <v>0.01310668459614415</v>
       </c>
       <c r="J11" t="n">
         <v>4.371875</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3805147058823524</v>
+        <v>0.4821691176470591</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -932,19 +932,19 @@
         <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>3.359742647058824</v>
+        <v>3.408639705882353</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5410384886694074</v>
+        <v>0.7172720959879871</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09564299605526475</v>
+        <v>0.1267969907572485</v>
       </c>
       <c r="J12" t="n">
         <v>1.887683823529412</v>
       </c>
       <c r="K12" t="n">
-        <v>1.472058823529412</v>
+        <v>1.520955882352942</v>
       </c>
     </row>
     <row r="13">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -975,19 +975,19 @@
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>4.247426470588236</v>
+        <v>4.424264705882353</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1967757603336715</v>
+        <v>0.2445465015192218</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0347853686262695</v>
+        <v>0.04323012238492201</v>
       </c>
       <c r="J13" t="n">
         <v>2.629963235294118</v>
       </c>
       <c r="K13" t="n">
-        <v>1.617463235294118</v>
+        <v>1.794301470588235</v>
       </c>
     </row>
     <row r="14">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1792,19 +1792,19 @@
         <v>32</v>
       </c>
       <c r="G32" t="n">
-        <v>4.3203125</v>
+        <v>4.372395833333334</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1060646971526287</v>
+        <v>0.1304533984137865</v>
       </c>
       <c r="I32" t="n">
-        <v>0.01874976665028032</v>
+        <v>0.02306112066180471</v>
       </c>
       <c r="J32" t="n">
         <v>4.15625</v>
       </c>
       <c r="K32" t="n">
-        <v>0.1640625</v>
+        <v>0.2161458333333339</v>
       </c>
     </row>
     <row r="33">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1835,19 +1835,19 @@
         <v>32</v>
       </c>
       <c r="G33" t="n">
-        <v>2.471354166666667</v>
+        <v>2.677083333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5546356351011124</v>
+        <v>0.4867187702260132</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09804665466692601</v>
+        <v>0.08604053573939774</v>
       </c>
       <c r="J33" t="n">
         <v>1.786458333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6848958333333333</v>
+        <v>0.8906249999999998</v>
       </c>
     </row>
     <row r="34">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1878,19 +1878,19 @@
         <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>3.598958333333333</v>
+        <v>3.578125</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3288934826643242</v>
+        <v>0.2783540170023813</v>
       </c>
       <c r="I34" t="n">
-        <v>0.05814070297000095</v>
+        <v>0.04920650324822484</v>
       </c>
       <c r="J34" t="n">
         <v>2.627604166666667</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9713541666666665</v>
+        <v>0.9505208333333335</v>
       </c>
     </row>
     <row r="35">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1921,19 +1921,19 @@
         <v>32</v>
       </c>
       <c r="G35" t="n">
-        <v>4.263020833333334</v>
+        <v>4.372395833333334</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1254193235527528</v>
+        <v>0.1304533984137865</v>
       </c>
       <c r="I35" t="n">
-        <v>0.02217121354399529</v>
+        <v>0.02306112066180471</v>
       </c>
       <c r="J35" t="n">
         <v>4.15625</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1067708333333339</v>
+        <v>0.2161458333333339</v>
       </c>
     </row>
     <row r="36">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1964,19 +1964,19 @@
         <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>2.6328125</v>
+        <v>2.677083333333333</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4967904943242132</v>
+        <v>0.4867187702260132</v>
       </c>
       <c r="I36" t="n">
-        <v>0.08782098184141704</v>
+        <v>0.08604053573939774</v>
       </c>
       <c r="J36" t="n">
         <v>1.786458333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8463541666666667</v>
+        <v>0.8906249999999998</v>
       </c>
     </row>
     <row r="37">
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2007,19 +2007,19 @@
         <v>32</v>
       </c>
       <c r="G37" t="n">
-        <v>3.427083333333333</v>
+        <v>3.578125</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4403230729840881</v>
+        <v>0.2783540170023813</v>
       </c>
       <c r="I37" t="n">
-        <v>0.07783885770498694</v>
+        <v>0.04920650324822484</v>
       </c>
       <c r="J37" t="n">
         <v>2.627604166666667</v>
       </c>
       <c r="K37" t="n">
-        <v>0.7994791666666665</v>
+        <v>0.9505208333333335</v>
       </c>
     </row>
     <row r="38">
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2824,19 +2824,19 @@
         <v>32</v>
       </c>
       <c r="G56" t="n">
-        <v>3.99609375</v>
+        <v>4</v>
       </c>
       <c r="H56" t="n">
-        <v>0.02209708691207961</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0.00390625</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>3.9140625</v>
       </c>
       <c r="K56" t="n">
-        <v>0.08203125</v>
+        <v>0.0859375</v>
       </c>
     </row>
     <row r="57">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2867,19 +2867,19 @@
         <v>32</v>
       </c>
       <c r="G57" t="n">
-        <v>1.78515625</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>0.7015495342396968</v>
+        <v>0.6659942845826639</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1240176082497884</v>
+        <v>0.1177322687149712</v>
       </c>
       <c r="J57" t="n">
         <v>1.08203125</v>
       </c>
       <c r="K57" t="n">
-        <v>0.703125</v>
+        <v>0.91796875</v>
       </c>
     </row>
     <row r="58">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2910,19 +2910,19 @@
         <v>32</v>
       </c>
       <c r="G58" t="n">
-        <v>2.94140625</v>
+        <v>2.8046875</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2519768114491183</v>
+        <v>0.2374628578766956</v>
       </c>
       <c r="I58" t="n">
-        <v>0.04454362801935891</v>
+        <v>0.0419778992711372</v>
       </c>
       <c r="J58" t="n">
         <v>2.0703125</v>
       </c>
       <c r="K58" t="n">
-        <v>0.87109375</v>
+        <v>0.734375</v>
       </c>
     </row>
     <row r="59">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2996,19 +2996,19 @@
         <v>32</v>
       </c>
       <c r="G60" t="n">
-        <v>2.0234375</v>
+        <v>2</v>
       </c>
       <c r="H60" t="n">
-        <v>0.566573511871883</v>
+        <v>0.6659942845826639</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1001569930713213</v>
+        <v>0.1177322687149712</v>
       </c>
       <c r="J60" t="n">
         <v>1.08203125</v>
       </c>
       <c r="K60" t="n">
-        <v>0.94140625</v>
+        <v>0.91796875</v>
       </c>
     </row>
     <row r="61">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3039,19 +3039,19 @@
         <v>32</v>
       </c>
       <c r="G61" t="n">
-        <v>2.73828125</v>
+        <v>2.8046875</v>
       </c>
       <c r="H61" t="n">
-        <v>0.443773426233078</v>
+        <v>0.2374628578766956</v>
       </c>
       <c r="I61" t="n">
-        <v>0.07844879974994939</v>
+        <v>0.0419778992711372</v>
       </c>
       <c r="J61" t="n">
         <v>2.0703125</v>
       </c>
       <c r="K61" t="n">
-        <v>0.66796875</v>
+        <v>0.734375</v>
       </c>
     </row>
     <row r="62">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3856,19 +3856,19 @@
         <v>32</v>
       </c>
       <c r="G80" t="n">
-        <v>4.635416666666667</v>
+        <v>4.682291666666667</v>
       </c>
       <c r="H80" t="n">
-        <v>0.09871486036009985</v>
+        <v>0.06502515366624655</v>
       </c>
       <c r="I80" t="n">
-        <v>0.01745048679112743</v>
+        <v>0.01149493177627506</v>
       </c>
       <c r="J80" t="n">
         <v>4.541666666666667</v>
       </c>
       <c r="K80" t="n">
-        <v>0.09375</v>
+        <v>0.140625</v>
       </c>
     </row>
     <row r="81">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3899,19 +3899,19 @@
         <v>32</v>
       </c>
       <c r="G81" t="n">
-        <v>2.296875</v>
+        <v>2.692708333333333</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8997554177819419</v>
+        <v>0.8520577821707317</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1590557893307366</v>
+        <v>0.1506239589339236</v>
       </c>
       <c r="J81" t="n">
         <v>1.291666666666667</v>
       </c>
       <c r="K81" t="n">
-        <v>1.005208333333333</v>
+        <v>1.401041666666666</v>
       </c>
     </row>
     <row r="82">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3942,19 +3942,19 @@
         <v>32</v>
       </c>
       <c r="G82" t="n">
-        <v>3.744791666666667</v>
+        <v>3.671875</v>
       </c>
       <c r="H82" t="n">
-        <v>0.2807579826164653</v>
+        <v>0.2412793522174072</v>
       </c>
       <c r="I82" t="n">
-        <v>0.04963146834508936</v>
+        <v>0.04265256652830652</v>
       </c>
       <c r="J82" t="n">
         <v>2.614583333333333</v>
       </c>
       <c r="K82" t="n">
-        <v>1.130208333333333</v>
+        <v>1.057291666666667</v>
       </c>
     </row>
     <row r="83">
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3985,19 +3985,19 @@
         <v>32</v>
       </c>
       <c r="G83" t="n">
-        <v>4.635416666666667</v>
+        <v>4.682291666666667</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0891768409430021</v>
+        <v>0.06502515366624655</v>
       </c>
       <c r="I83" t="n">
-        <v>0.01576438723889773</v>
+        <v>0.01149493177627506</v>
       </c>
       <c r="J83" t="n">
         <v>4.541666666666667</v>
       </c>
       <c r="K83" t="n">
-        <v>0.09375</v>
+        <v>0.140625</v>
       </c>
     </row>
     <row r="84">
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4028,19 +4028,19 @@
         <v>32</v>
       </c>
       <c r="G84" t="n">
-        <v>2.671875</v>
+        <v>2.692708333333333</v>
       </c>
       <c r="H84" t="n">
-        <v>0.7660871758043595</v>
+        <v>0.8520577821707317</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1354263592478283</v>
+        <v>0.1506239589339236</v>
       </c>
       <c r="J84" t="n">
         <v>1.291666666666667</v>
       </c>
       <c r="K84" t="n">
-        <v>1.380208333333333</v>
+        <v>1.401041666666666</v>
       </c>
     </row>
     <row r="85">
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4071,19 +4071,19 @@
         <v>32</v>
       </c>
       <c r="G85" t="n">
-        <v>3.557291666666667</v>
+        <v>3.671875</v>
       </c>
       <c r="H85" t="n">
-        <v>0.5657636305588073</v>
+        <v>0.2412793522174072</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1000138249292133</v>
+        <v>0.04265256652830652</v>
       </c>
       <c r="J85" t="n">
         <v>2.614583333333333</v>
       </c>
       <c r="K85" t="n">
-        <v>0.9427083333333339</v>
+        <v>1.057291666666667</v>
       </c>
     </row>
     <row r="86">
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4888,19 +4888,19 @@
         <v>32</v>
       </c>
       <c r="G104" t="n">
-        <v>4.4453125</v>
+        <v>4.578125</v>
       </c>
       <c r="H104" t="n">
-        <v>0.1050033601612886</v>
+        <v>0.249495458617923</v>
       </c>
       <c r="I104" t="n">
-        <v>0.01856214700435514</v>
+        <v>0.04410498266599525</v>
       </c>
       <c r="J104" t="n">
         <v>4.1640625</v>
       </c>
       <c r="K104" t="n">
-        <v>0.28125</v>
+        <v>0.4140625</v>
       </c>
     </row>
     <row r="105">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4931,19 +4931,19 @@
         <v>32</v>
       </c>
       <c r="G105" t="n">
-        <v>3.3046875</v>
+        <v>3.6640625</v>
       </c>
       <c r="H105" t="n">
-        <v>0.6309694761545203</v>
+        <v>0.587536460776636</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1115406988276462</v>
+        <v>0.1038627539023758</v>
       </c>
       <c r="J105" t="n">
         <v>2.234375</v>
       </c>
       <c r="K105" t="n">
-        <v>1.0703125</v>
+        <v>1.4296875</v>
       </c>
     </row>
     <row r="106">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4974,19 +4974,19 @@
         <v>32</v>
       </c>
       <c r="G106" t="n">
-        <v>4.28125</v>
+        <v>4.5078125</v>
       </c>
       <c r="H106" t="n">
-        <v>0.267530522829006</v>
+        <v>0.2802963221767393</v>
       </c>
       <c r="I106" t="n">
-        <v>0.04729316171669314</v>
+        <v>0.04954985753820541</v>
       </c>
       <c r="J106" t="n">
         <v>2.9609375</v>
       </c>
       <c r="K106" t="n">
-        <v>1.3203125</v>
+        <v>1.546875</v>
       </c>
     </row>
     <row r="107">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -5017,19 +5017,19 @@
         <v>32</v>
       </c>
       <c r="G107" t="n">
-        <v>4.453125</v>
+        <v>4.578125</v>
       </c>
       <c r="H107" t="n">
-        <v>0.1480722905401495</v>
+        <v>0.249495458617923</v>
       </c>
       <c r="I107" t="n">
-        <v>0.0261757301866911</v>
+        <v>0.04410498266599525</v>
       </c>
       <c r="J107" t="n">
         <v>4.1640625</v>
       </c>
       <c r="K107" t="n">
-        <v>0.2890625</v>
+        <v>0.4140625</v>
       </c>
     </row>
     <row r="108">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5060,19 +5060,19 @@
         <v>32</v>
       </c>
       <c r="G108" t="n">
-        <v>3.640625</v>
+        <v>3.6640625</v>
       </c>
       <c r="H108" t="n">
-        <v>0.448732534029765</v>
+        <v>0.587536460776636</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0793254544378675</v>
+        <v>0.1038627539023758</v>
       </c>
       <c r="J108" t="n">
         <v>2.234375</v>
       </c>
       <c r="K108" t="n">
-        <v>1.40625</v>
+        <v>1.4296875</v>
       </c>
     </row>
     <row r="109">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -5103,19 +5103,19 @@
         <v>32</v>
       </c>
       <c r="G109" t="n">
-        <v>4.15625</v>
+        <v>4.5078125</v>
       </c>
       <c r="H109" t="n">
-        <v>0.3521248862035612</v>
+        <v>0.2802963221767393</v>
       </c>
       <c r="I109" t="n">
-        <v>0.06224747371476988</v>
+        <v>0.04954985753820541</v>
       </c>
       <c r="J109" t="n">
         <v>2.9609375</v>
       </c>
       <c r="K109" t="n">
-        <v>1.1953125</v>
+        <v>1.546875</v>
       </c>
     </row>
     <row r="110">
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5920,19 +5920,19 @@
         <v>32</v>
       </c>
       <c r="G128" t="n">
-        <v>0.8295882936507937</v>
+        <v>0.8569006099576753</v>
       </c>
       <c r="H128" t="n">
-        <v>0.07133669757790652</v>
+        <v>0.05900058772222223</v>
       </c>
       <c r="I128" t="n">
-        <v>0.01261066565119791</v>
+        <v>0.01042992891809377</v>
       </c>
       <c r="J128" t="n">
         <v>0.8269659801249475</v>
       </c>
       <c r="K128" t="n">
-        <v>0.002622313525846187</v>
+        <v>0.02993462983272777</v>
       </c>
     </row>
     <row r="129">
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5963,19 +5963,19 @@
         <v>32</v>
       </c>
       <c r="G129" t="n">
-        <v>0.2769444964757465</v>
+        <v>0.3619417686693102</v>
       </c>
       <c r="H129" t="n">
-        <v>0.2407157582411586</v>
+        <v>0.2396955014699558</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0425529362476962</v>
+        <v>0.04237257862732895</v>
       </c>
       <c r="J129" t="n">
         <v>0.14071079687856</v>
       </c>
       <c r="K129" t="n">
-        <v>0.1362336995971865</v>
+        <v>0.2212309717907502</v>
       </c>
     </row>
     <row r="130">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -6006,19 +6006,19 @@
         <v>32</v>
       </c>
       <c r="G130" t="n">
-        <v>0.6281098037991421</v>
+        <v>0.656460424185303</v>
       </c>
       <c r="H130" t="n">
-        <v>0.04111854636761736</v>
+        <v>0.07324949339596523</v>
       </c>
       <c r="I130" t="n">
-        <v>0.007268800742268928</v>
+        <v>0.01294880337469156</v>
       </c>
       <c r="J130" t="n">
         <v>0.4445382507163197</v>
       </c>
       <c r="K130" t="n">
-        <v>0.1835715530828223</v>
+        <v>0.2119221734689833</v>
       </c>
     </row>
     <row r="131">
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -6049,19 +6049,19 @@
         <v>32</v>
       </c>
       <c r="G131" t="n">
-        <v>0.8494941364226851</v>
+        <v>0.8569006099576753</v>
       </c>
       <c r="H131" t="n">
-        <v>0.06090605493155651</v>
+        <v>0.05900058772222223</v>
       </c>
       <c r="I131" t="n">
-        <v>0.01076677111435599</v>
+        <v>0.01042992891809377</v>
       </c>
       <c r="J131" t="n">
         <v>0.8269659801249475</v>
       </c>
       <c r="K131" t="n">
-        <v>0.02252815629773763</v>
+        <v>0.02993462983272777</v>
       </c>
     </row>
     <row r="132">
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -6092,19 +6092,19 @@
         <v>32</v>
       </c>
       <c r="G132" t="n">
-        <v>0.3842922278100296</v>
+        <v>0.3619417686693102</v>
       </c>
       <c r="H132" t="n">
-        <v>0.2134404946473891</v>
+        <v>0.2396955014699558</v>
       </c>
       <c r="I132" t="n">
-        <v>0.03773130528624496</v>
+        <v>0.04237257862732895</v>
       </c>
       <c r="J132" t="n">
         <v>0.14071079687856</v>
       </c>
       <c r="K132" t="n">
-        <v>0.2435814309314696</v>
+        <v>0.2212309717907502</v>
       </c>
     </row>
     <row r="133">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -6135,19 +6135,19 @@
         <v>32</v>
       </c>
       <c r="G133" t="n">
-        <v>0.6074824481074481</v>
+        <v>0.656460424185303</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1191206822662597</v>
+        <v>0.07324949339596523</v>
       </c>
       <c r="I133" t="n">
-        <v>0.02105776055251009</v>
+        <v>0.01294880337469156</v>
       </c>
       <c r="J133" t="n">
         <v>0.4445382507163197</v>
       </c>
       <c r="K133" t="n">
-        <v>0.1629441973911284</v>
+        <v>0.2119221734689833</v>
       </c>
     </row>
     <row r="134">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -6952,19 +6952,19 @@
         <v>32</v>
       </c>
       <c r="G152" t="n">
-        <v>0.3339020788239538</v>
+        <v>0.2788451479076479</v>
       </c>
       <c r="H152" t="n">
-        <v>0.2021232147137728</v>
+        <v>0.1458108650348325</v>
       </c>
       <c r="I152" t="n">
-        <v>0.03573067393983332</v>
+        <v>0.02577596285920162</v>
       </c>
       <c r="J152" t="n">
         <v>0.2408584731240981</v>
       </c>
       <c r="K152" t="n">
-        <v>0.09304360569985573</v>
+        <v>0.03798667478354975</v>
       </c>
     </row>
     <row r="153">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -6995,19 +6995,19 @@
         <v>32</v>
       </c>
       <c r="G153" t="n">
-        <v>0.3213367842861529</v>
+        <v>0.2641779906432576</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1716668315951759</v>
+        <v>0.1372888643130128</v>
       </c>
       <c r="I153" t="n">
-        <v>0.03034669518143949</v>
+        <v>0.02426947173428279</v>
       </c>
       <c r="J153" t="n">
         <v>0.2097223436285936</v>
       </c>
       <c r="K153" t="n">
-        <v>0.1116144406575593</v>
+        <v>0.05445564701466402</v>
       </c>
     </row>
     <row r="154">
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -7038,19 +7038,19 @@
         <v>32</v>
       </c>
       <c r="G154" t="n">
-        <v>0.3656164148351648</v>
+        <v>0.3008668097809259</v>
       </c>
       <c r="H154" t="n">
-        <v>0.2489829900539111</v>
+        <v>0.1757768738896749</v>
       </c>
       <c r="I154" t="n">
-        <v>0.04401439016680581</v>
+        <v>0.03107325487579043</v>
       </c>
       <c r="J154" t="n">
         <v>0.1764841321872572</v>
       </c>
       <c r="K154" t="n">
-        <v>0.1891322826479077</v>
+        <v>0.1243826775936687</v>
       </c>
     </row>
     <row r="155">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -7081,19 +7081,19 @@
         <v>32</v>
       </c>
       <c r="G155" t="n">
-        <v>0.3180535130718954</v>
+        <v>0.2788451479076479</v>
       </c>
       <c r="H155" t="n">
-        <v>0.2119084470935038</v>
+        <v>0.1458108650348325</v>
       </c>
       <c r="I155" t="n">
-        <v>0.03746047498263181</v>
+        <v>0.02577596285920162</v>
       </c>
       <c r="J155" t="n">
         <v>0.2408584731240981</v>
       </c>
       <c r="K155" t="n">
-        <v>0.07719503994779733</v>
+        <v>0.03798667478354975</v>
       </c>
     </row>
     <row r="156">
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -7124,19 +7124,19 @@
         <v>32</v>
       </c>
       <c r="G156" t="n">
-        <v>0.3049718163780664</v>
+        <v>0.2641779906432576</v>
       </c>
       <c r="H156" t="n">
-        <v>0.1469723183733395</v>
+        <v>0.1372888643130128</v>
       </c>
       <c r="I156" t="n">
-        <v>0.02598128074212414</v>
+        <v>0.02426947173428279</v>
       </c>
       <c r="J156" t="n">
         <v>0.2097223436285936</v>
       </c>
       <c r="K156" t="n">
-        <v>0.09524947274947274</v>
+        <v>0.05445564701466402</v>
       </c>
     </row>
     <row r="157">
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -7167,19 +7167,19 @@
         <v>32</v>
       </c>
       <c r="G157" t="n">
-        <v>0.2919101333715304</v>
+        <v>0.3008668097809259</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1763362746727831</v>
+        <v>0.1757768738896749</v>
       </c>
       <c r="I157" t="n">
-        <v>0.03117214389757465</v>
+        <v>0.03107325487579043</v>
       </c>
       <c r="J157" t="n">
         <v>0.1764841321872572</v>
       </c>
       <c r="K157" t="n">
-        <v>0.1154260011842733</v>
+        <v>0.1243826775936687</v>
       </c>
     </row>
     <row r="158">
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -7984,19 +7984,19 @@
         <v>32</v>
       </c>
       <c r="G176" t="n">
-        <v>4.9375</v>
+        <v>4.9875</v>
       </c>
       <c r="H176" t="n">
-        <v>0.1475608130513895</v>
+        <v>0.07071067811865481</v>
       </c>
       <c r="I176" t="n">
-        <v>0.02608531288650949</v>
+        <v>0.01250000000000001</v>
       </c>
       <c r="J176" t="n">
         <v>4.4625</v>
       </c>
       <c r="K176" t="n">
-        <v>0.4749999999999996</v>
+        <v>0.5249999999999995</v>
       </c>
     </row>
     <row r="177">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -8027,19 +8027,19 @@
         <v>32</v>
       </c>
       <c r="G177" t="n">
-        <v>2.8</v>
+        <v>3.2125</v>
       </c>
       <c r="H177" t="n">
-        <v>0.842423539174232</v>
+        <v>0.801510670445946</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1489208492953176</v>
+        <v>0.1416884075664261</v>
       </c>
       <c r="J177" t="n">
         <v>1.7</v>
       </c>
       <c r="K177" t="n">
-        <v>1.1</v>
+        <v>1.5125</v>
       </c>
     </row>
     <row r="178">
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -8070,19 +8070,19 @@
         <v>32</v>
       </c>
       <c r="G178" t="n">
-        <v>4.225000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="H178" t="n">
-        <v>0.257782103535575</v>
+        <v>0.2782433374561009</v>
       </c>
       <c r="I178" t="n">
-        <v>0.04556986836963443</v>
+        <v>0.04918693768379645</v>
       </c>
       <c r="J178" t="n">
         <v>2.56875</v>
       </c>
       <c r="K178" t="n">
-        <v>1.65625</v>
+        <v>1.83125</v>
       </c>
     </row>
     <row r="179">
@@ -8102,7 +8102,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -8113,19 +8113,19 @@
         <v>32</v>
       </c>
       <c r="G179" t="n">
-        <v>4.93125</v>
+        <v>4.9875</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1490561704039249</v>
+        <v>0.07071067811865481</v>
       </c>
       <c r="I179" t="n">
-        <v>0.02634965721757822</v>
+        <v>0.01250000000000001</v>
       </c>
       <c r="J179" t="n">
         <v>4.4625</v>
       </c>
       <c r="K179" t="n">
-        <v>0.46875</v>
+        <v>0.5249999999999995</v>
       </c>
     </row>
     <row r="180">
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -8156,19 +8156,19 @@
         <v>32</v>
       </c>
       <c r="G180" t="n">
-        <v>3.1625</v>
+        <v>3.2125</v>
       </c>
       <c r="H180" t="n">
-        <v>0.6020127530532137</v>
+        <v>0.801510670445946</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1064218250111774</v>
+        <v>0.1416884075664261</v>
       </c>
       <c r="J180" t="n">
         <v>1.7</v>
       </c>
       <c r="K180" t="n">
-        <v>1.4625</v>
+        <v>1.5125</v>
       </c>
     </row>
     <row r="181">
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -8199,19 +8199,19 @@
         <v>32</v>
       </c>
       <c r="G181" t="n">
-        <v>4.20625</v>
+        <v>4.4</v>
       </c>
       <c r="H181" t="n">
-        <v>0.2408821154597973</v>
+        <v>0.2782433374561009</v>
       </c>
       <c r="I181" t="n">
-        <v>0.04258234432704589</v>
+        <v>0.04918693768379645</v>
       </c>
       <c r="J181" t="n">
         <v>2.56875</v>
       </c>
       <c r="K181" t="n">
-        <v>1.6375</v>
+        <v>1.83125</v>
       </c>
     </row>
     <row r="182">
@@ -9005,7 +9005,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -9016,19 +9016,19 @@
         <v>32</v>
       </c>
       <c r="G200" t="n">
-        <v>4.656249999999999</v>
+        <v>4.720588235294118</v>
       </c>
       <c r="H200" t="n">
-        <v>0.1242091850188243</v>
+        <v>0.1097948853243979</v>
       </c>
       <c r="I200" t="n">
-        <v>0.02195728925311629</v>
+        <v>0.01940917698812028</v>
       </c>
       <c r="J200" t="n">
         <v>4.28125</v>
       </c>
       <c r="K200" t="n">
-        <v>0.3749999999999991</v>
+        <v>0.4393382352941178</v>
       </c>
     </row>
     <row r="201">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -9059,19 +9059,19 @@
         <v>32</v>
       </c>
       <c r="G201" t="n">
-        <v>3.275735294117647</v>
+        <v>3.604779411764706</v>
       </c>
       <c r="H201" t="n">
-        <v>0.7260615815809258</v>
+        <v>0.66033209891481</v>
       </c>
       <c r="I201" t="n">
-        <v>0.1283507669737256</v>
+        <v>0.1167313262444521</v>
       </c>
       <c r="J201" t="n">
         <v>2.075367647058823</v>
       </c>
       <c r="K201" t="n">
-        <v>1.200367647058823</v>
+        <v>1.529411764705882</v>
       </c>
     </row>
     <row r="202">
@@ -9091,7 +9091,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -9102,19 +9102,19 @@
         <v>32</v>
       </c>
       <c r="G202" t="n">
-        <v>4.354779411764706</v>
+        <v>4.448529411764706</v>
       </c>
       <c r="H202" t="n">
-        <v>0.1389485615506837</v>
+        <v>0.2274547972372718</v>
       </c>
       <c r="I202" t="n">
-        <v>0.02456286752715121</v>
+        <v>0.04020870738497152</v>
       </c>
       <c r="J202" t="n">
         <v>2.691176470588236</v>
       </c>
       <c r="K202" t="n">
-        <v>1.66360294117647</v>
+        <v>1.75735294117647</v>
       </c>
     </row>
     <row r="203">
@@ -9134,7 +9134,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -9145,19 +9145,19 @@
         <v>32</v>
       </c>
       <c r="G203" t="n">
-        <v>4.573529411764707</v>
+        <v>4.720588235294118</v>
       </c>
       <c r="H203" t="n">
-        <v>0.112803521424682</v>
+        <v>0.1097948853243979</v>
       </c>
       <c r="I203" t="n">
-        <v>0.01994103373527865</v>
+        <v>0.01940917698812028</v>
       </c>
       <c r="J203" t="n">
         <v>4.28125</v>
       </c>
       <c r="K203" t="n">
-        <v>0.2922794117647065</v>
+        <v>0.4393382352941178</v>
       </c>
     </row>
     <row r="204">
@@ -9177,7 +9177,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -9188,19 +9188,19 @@
         <v>32</v>
       </c>
       <c r="G204" t="n">
-        <v>3.556985294117647</v>
+        <v>3.604779411764706</v>
       </c>
       <c r="H204" t="n">
-        <v>0.506015686722543</v>
+        <v>0.66033209891481</v>
       </c>
       <c r="I204" t="n">
-        <v>0.08945178086706945</v>
+        <v>0.1167313262444521</v>
       </c>
       <c r="J204" t="n">
         <v>2.075367647058823</v>
       </c>
       <c r="K204" t="n">
-        <v>1.481617647058824</v>
+        <v>1.529411764705882</v>
       </c>
     </row>
     <row r="205">
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -9231,19 +9231,19 @@
         <v>32</v>
       </c>
       <c r="G205" t="n">
-        <v>4.28860294117647</v>
+        <v>4.448529411764706</v>
       </c>
       <c r="H205" t="n">
-        <v>0.1838187855175352</v>
+        <v>0.2274547972372718</v>
       </c>
       <c r="I205" t="n">
-        <v>0.03249487743723117</v>
+        <v>0.04020870738497152</v>
       </c>
       <c r="J205" t="n">
         <v>2.691176470588236</v>
       </c>
       <c r="K205" t="n">
-        <v>1.597426470588235</v>
+        <v>1.75735294117647</v>
       </c>
     </row>
     <row r="206">
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -10033,19 +10033,19 @@
         <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>4.050857843137256</v>
+        <v>4.308946078431373</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8753989547745467</v>
+        <v>0.6423528833928527</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1263529555468504</v>
+        <v>0.09271565253539896</v>
       </c>
       <c r="J6" t="n">
         <v>2.971813725490196</v>
       </c>
       <c r="K6" t="n">
-        <v>1.079044117647059</v>
+        <v>1.337132352941177</v>
       </c>
     </row>
     <row r="7">
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -10076,19 +10076,19 @@
         <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>4.032230392156863</v>
+        <v>4.149019607843138</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8778231574005128</v>
+        <v>0.8407683732509679</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1267028590565183</v>
+        <v>0.1213544616556425</v>
       </c>
       <c r="J7" t="n">
         <v>2.95453431372549</v>
       </c>
       <c r="K7" t="n">
-        <v>1.077696078431372</v>
+        <v>1.194485294117647</v>
       </c>
     </row>
     <row r="8">
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -10119,19 +10119,19 @@
         <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>4.128676470588236</v>
+        <v>4.308946078431373</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6485142636846617</v>
+        <v>0.6423528833928527</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09360497117791285</v>
+        <v>0.09271565253539896</v>
       </c>
       <c r="J8" t="n">
         <v>2.971813725490196</v>
       </c>
       <c r="K8" t="n">
-        <v>1.156862745098039</v>
+        <v>1.337132352941177</v>
       </c>
     </row>
     <row r="9">
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -10162,19 +10162,19 @@
         <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>4.111029411764705</v>
+        <v>4.149019607843138</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6936610205468139</v>
+        <v>0.8407683732509679</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1001213442347634</v>
+        <v>0.1213544616556425</v>
       </c>
       <c r="J9" t="n">
         <v>2.95453431372549</v>
       </c>
       <c r="K9" t="n">
-        <v>1.156495098039215</v>
+        <v>1.194485294117647</v>
       </c>
     </row>
     <row r="10">
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -10721,19 +10721,19 @@
         <v>48</v>
       </c>
       <c r="G22" t="n">
-        <v>3.472222222222222</v>
+        <v>3.600694444444444</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8722022704799717</v>
+        <v>0.7211672828151556</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1258915539123536</v>
+        <v>0.1040915312160203</v>
       </c>
       <c r="J22" t="n">
         <v>2.828125</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6440972222222219</v>
+        <v>0.7725694444444442</v>
       </c>
     </row>
     <row r="23">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -10764,19 +10764,19 @@
         <v>48</v>
       </c>
       <c r="G23" t="n">
-        <v>3.454861111111111</v>
+        <v>3.484375</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8386282727327019</v>
+        <v>0.8193248550392612</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1210455647530641</v>
+        <v>0.1182593564026671</v>
       </c>
       <c r="J23" t="n">
         <v>2.885416666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5694444444444446</v>
+        <v>0.5989583333333335</v>
       </c>
     </row>
     <row r="24">
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -10807,19 +10807,19 @@
         <v>48</v>
       </c>
       <c r="G24" t="n">
-        <v>3.375</v>
+        <v>3.600694444444444</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7855070188074355</v>
+        <v>0.7211672828151556</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1133781721897033</v>
+        <v>0.1040915312160203</v>
       </c>
       <c r="J24" t="n">
         <v>2.828125</v>
       </c>
       <c r="K24" t="n">
-        <v>0.546875</v>
+        <v>0.7725694444444442</v>
       </c>
     </row>
     <row r="25">
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -10850,19 +10850,19 @@
         <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>3.506944444444444</v>
+        <v>3.484375</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7615992981468315</v>
+        <v>0.8193248550392612</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1099273899499258</v>
+        <v>0.1182593564026671</v>
       </c>
       <c r="J25" t="n">
         <v>2.885416666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6215277777777777</v>
+        <v>0.5989583333333335</v>
       </c>
     </row>
     <row r="26">
@@ -11398,7 +11398,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -11409,19 +11409,19 @@
         <v>48</v>
       </c>
       <c r="G38" t="n">
-        <v>2.919270833333333</v>
+        <v>3.005208333333333</v>
       </c>
       <c r="H38" t="n">
-        <v>1.005136271899812</v>
+        <v>0.8454187923137049</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1450789242884033</v>
+        <v>0.1220256918300715</v>
       </c>
       <c r="J38" t="n">
         <v>2.317708333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6015625</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="39">
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -11452,19 +11452,19 @@
         <v>48</v>
       </c>
       <c r="G39" t="n">
-        <v>2.895833333333333</v>
+        <v>2.864583333333333</v>
       </c>
       <c r="H39" t="n">
-        <v>1.010691954529348</v>
+        <v>0.9919333332380017</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1458808180038271</v>
+        <v>0.1431732442407808</v>
       </c>
       <c r="J39" t="n">
         <v>2.393229166666667</v>
       </c>
       <c r="K39" t="n">
-        <v>0.502604166666667</v>
+        <v>0.471354166666667</v>
       </c>
     </row>
     <row r="40">
@@ -11484,7 +11484,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -11495,19 +11495,19 @@
         <v>48</v>
       </c>
       <c r="G40" t="n">
-        <v>2.8828125</v>
+        <v>3.005208333333333</v>
       </c>
       <c r="H40" t="n">
-        <v>0.898212708927414</v>
+        <v>0.8454187923137049</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1296458373221964</v>
+        <v>0.1220256918300715</v>
       </c>
       <c r="J40" t="n">
         <v>2.317708333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5651041666666665</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="41">
@@ -11527,7 +11527,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -11538,19 +11538,19 @@
         <v>48</v>
       </c>
       <c r="G41" t="n">
-        <v>2.958333333333333</v>
+        <v>2.864583333333333</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9464847243000457</v>
+        <v>0.9919333332380017</v>
       </c>
       <c r="I41" t="n">
-        <v>0.136613302589625</v>
+        <v>0.1431732442407808</v>
       </c>
       <c r="J41" t="n">
         <v>2.393229166666667</v>
       </c>
       <c r="K41" t="n">
-        <v>0.565104166666667</v>
+        <v>0.471354166666667</v>
       </c>
     </row>
     <row r="42">
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -12097,19 +12097,19 @@
         <v>48</v>
       </c>
       <c r="G54" t="n">
-        <v>3.572916666666667</v>
+        <v>3.78125</v>
       </c>
       <c r="H54" t="n">
-        <v>1.138155287572325</v>
+        <v>0.8840297335157641</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1642785654148695</v>
+        <v>0.1275987011542399</v>
       </c>
       <c r="J54" t="n">
         <v>2.784722222222222</v>
       </c>
       <c r="K54" t="n">
-        <v>0.7881944444444455</v>
+        <v>0.9965277777777781</v>
       </c>
     </row>
     <row r="55">
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -12140,19 +12140,19 @@
         <v>48</v>
       </c>
       <c r="G55" t="n">
-        <v>3.545138888888889</v>
+        <v>3.583333333333333</v>
       </c>
       <c r="H55" t="n">
-        <v>1.092495128948862</v>
+        <v>1.032566633892407</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1576880891967451</v>
+        <v>0.1490381560085018</v>
       </c>
       <c r="J55" t="n">
         <v>2.847222222222222</v>
       </c>
       <c r="K55" t="n">
-        <v>0.6979166666666674</v>
+        <v>0.7361111111111116</v>
       </c>
     </row>
     <row r="56">
@@ -12172,7 +12172,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -12183,19 +12183,19 @@
         <v>48</v>
       </c>
       <c r="G56" t="n">
-        <v>3.618055555555556</v>
+        <v>3.78125</v>
       </c>
       <c r="H56" t="n">
-        <v>0.952139765981734</v>
+        <v>0.8840297335157641</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1374295375489254</v>
+        <v>0.1275987011542399</v>
       </c>
       <c r="J56" t="n">
         <v>2.784722222222222</v>
       </c>
       <c r="K56" t="n">
-        <v>0.8333333333333339</v>
+        <v>0.9965277777777781</v>
       </c>
     </row>
     <row r="57">
@@ -12215,7 +12215,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -12226,19 +12226,19 @@
         <v>48</v>
       </c>
       <c r="G57" t="n">
-        <v>3.625</v>
+        <v>3.583333333333333</v>
       </c>
       <c r="H57" t="n">
-        <v>1.00677374847314</v>
+        <v>1.032566633892407</v>
       </c>
       <c r="I57" t="n">
-        <v>0.145315273673504</v>
+        <v>0.1490381560085018</v>
       </c>
       <c r="J57" t="n">
         <v>2.847222222222222</v>
       </c>
       <c r="K57" t="n">
-        <v>0.7777777777777781</v>
+        <v>0.7361111111111116</v>
       </c>
     </row>
     <row r="58">
@@ -12774,7 +12774,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -12785,19 +12785,19 @@
         <v>48</v>
       </c>
       <c r="G70" t="n">
-        <v>4.020833333333333</v>
+        <v>4.317708333333333</v>
       </c>
       <c r="H70" t="n">
-        <v>0.5966068356229727</v>
+        <v>0.4633928510423559</v>
       </c>
       <c r="I70" t="n">
-        <v>0.08611277928682352</v>
+        <v>0.0668849968224631</v>
       </c>
       <c r="J70" t="n">
         <v>3.114583333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>0.9062499999999996</v>
+        <v>1.203125</v>
       </c>
     </row>
     <row r="71">
@@ -12817,7 +12817,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -12828,19 +12828,19 @@
         <v>48</v>
       </c>
       <c r="G71" t="n">
-        <v>4</v>
+        <v>4.182291666666667</v>
       </c>
       <c r="H71" t="n">
-        <v>0.6918984060216639</v>
+        <v>0.6699070738458077</v>
       </c>
       <c r="I71" t="n">
-        <v>0.09986693274212016</v>
+        <v>0.0966927573542279</v>
       </c>
       <c r="J71" t="n">
         <v>3.125</v>
       </c>
       <c r="K71" t="n">
-        <v>0.875</v>
+        <v>1.057291666666667</v>
       </c>
     </row>
     <row r="72">
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -12871,19 +12871,19 @@
         <v>48</v>
       </c>
       <c r="G72" t="n">
-        <v>4.104166666666667</v>
+        <v>4.317708333333333</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4340351654217606</v>
+        <v>0.4633928510423559</v>
       </c>
       <c r="I72" t="n">
-        <v>0.06264757989850431</v>
+        <v>0.0668849968224631</v>
       </c>
       <c r="J72" t="n">
         <v>3.114583333333333</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9895833333333335</v>
+        <v>1.203125</v>
       </c>
     </row>
     <row r="73">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -12914,19 +12914,19 @@
         <v>48</v>
       </c>
       <c r="G73" t="n">
-        <v>4.0625</v>
+        <v>4.182291666666667</v>
       </c>
       <c r="H73" t="n">
-        <v>0.5195640562150525</v>
+        <v>0.6699070738458077</v>
       </c>
       <c r="I73" t="n">
-        <v>0.07499261192925361</v>
+        <v>0.0966927573542279</v>
       </c>
       <c r="J73" t="n">
         <v>3.125</v>
       </c>
       <c r="K73" t="n">
-        <v>0.9375</v>
+        <v>1.057291666666667</v>
       </c>
     </row>
     <row r="74">
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -13473,19 +13473,19 @@
         <v>48</v>
       </c>
       <c r="G86" t="n">
-        <v>0.5809098887223887</v>
+        <v>0.6445138674198777</v>
       </c>
       <c r="H86" t="n">
-        <v>0.276121277346154</v>
+        <v>0.229354465554107</v>
       </c>
       <c r="I86" t="n">
-        <v>0.03985467345119633</v>
+        <v>0.0331044656068766</v>
       </c>
       <c r="J86" t="n">
         <v>0.464800525657892</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1161093630644967</v>
+        <v>0.1797133417619857</v>
       </c>
     </row>
     <row r="87">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -13516,19 +13516,19 @@
         <v>48</v>
       </c>
       <c r="G87" t="n">
-        <v>0.575518507228066</v>
+        <v>0.605688001121648</v>
       </c>
       <c r="H87" t="n">
-        <v>0.2700851394194227</v>
+        <v>0.2734229620700355</v>
       </c>
       <c r="I87" t="n">
-        <v>0.03898343198698033</v>
+        <v>0.03946520518843995</v>
       </c>
       <c r="J87" t="n">
         <v>0.4766761594886595</v>
       </c>
       <c r="K87" t="n">
-        <v>0.09884234773940648</v>
+        <v>0.1290118416329885</v>
       </c>
     </row>
     <row r="88">
@@ -13548,7 +13548,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -13559,19 +13559,19 @@
         <v>48</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6181219880988104</v>
+        <v>0.6445138674198777</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2346034586755727</v>
+        <v>0.229354465554107</v>
       </c>
       <c r="I88" t="n">
-        <v>0.03386209250478979</v>
+        <v>0.0331044656068766</v>
       </c>
       <c r="J88" t="n">
         <v>0.464800525657892</v>
       </c>
       <c r="K88" t="n">
-        <v>0.1533214624409183</v>
+        <v>0.1797133417619857</v>
       </c>
     </row>
     <row r="89">
@@ -13591,7 +13591,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -13602,19 +13602,19 @@
         <v>48</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6093905534612981</v>
+        <v>0.605688001121648</v>
       </c>
       <c r="H89" t="n">
-        <v>0.245945067202048</v>
+        <v>0.2734229620700355</v>
       </c>
       <c r="I89" t="n">
-        <v>0.03549911268874075</v>
+        <v>0.03946520518843995</v>
       </c>
       <c r="J89" t="n">
         <v>0.4766761594886595</v>
       </c>
       <c r="K89" t="n">
-        <v>0.1327143939726386</v>
+        <v>0.1290118416329885</v>
       </c>
     </row>
     <row r="90">
@@ -14150,7 +14150,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -14161,19 +14161,19 @@
         <v>48</v>
       </c>
       <c r="G102" t="n">
-        <v>0.3414934565026477</v>
+        <v>0.2764341183913552</v>
       </c>
       <c r="H102" t="n">
-        <v>0.2171812885210567</v>
+        <v>0.1384857643827544</v>
       </c>
       <c r="I102" t="n">
-        <v>0.03134741884764547</v>
+        <v>0.01998869833632858</v>
       </c>
       <c r="J102" t="n">
         <v>0.2023699506512006</v>
       </c>
       <c r="K102" t="n">
-        <v>0.139123505851447</v>
+        <v>0.07406416774015459</v>
       </c>
     </row>
     <row r="103">
@@ -14193,7 +14193,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -14204,19 +14204,19 @@
         <v>48</v>
       </c>
       <c r="G103" t="n">
-        <v>0.3390767287942</v>
+        <v>0.2861591804965324</v>
       </c>
       <c r="H103" t="n">
-        <v>0.202016143291675</v>
+        <v>0.1675466505440653</v>
       </c>
       <c r="I103" t="n">
-        <v>0.02915851867752464</v>
+        <v>0.02418327594835907</v>
       </c>
       <c r="J103" t="n">
         <v>0.2156733486420986</v>
       </c>
       <c r="K103" t="n">
-        <v>0.1234033801521014</v>
+        <v>0.07048583185443374</v>
       </c>
     </row>
     <row r="104">
@@ -14236,7 +14236,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -14247,19 +14247,19 @@
         <v>48</v>
       </c>
       <c r="G104" t="n">
-        <v>0.2647016957035339</v>
+        <v>0.2764341183913552</v>
       </c>
       <c r="H104" t="n">
-        <v>0.1285790495537913</v>
+        <v>0.1384857643827544</v>
       </c>
       <c r="I104" t="n">
-        <v>0.01855878721800692</v>
+        <v>0.01998869833632858</v>
       </c>
       <c r="J104" t="n">
         <v>0.2023699506512006</v>
       </c>
       <c r="K104" t="n">
-        <v>0.06233174505233327</v>
+        <v>0.07406416774015459</v>
       </c>
     </row>
     <row r="105">
@@ -14279,7 +14279,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -14290,19 +14290,19 @@
         <v>48</v>
       </c>
       <c r="G105" t="n">
-        <v>0.3452552795107942</v>
+        <v>0.2861591804965324</v>
       </c>
       <c r="H105" t="n">
-        <v>0.2115690209570757</v>
+        <v>0.1675466505440653</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0305373578004383</v>
+        <v>0.02418327594835907</v>
       </c>
       <c r="J105" t="n">
         <v>0.2156733486420986</v>
       </c>
       <c r="K105" t="n">
-        <v>0.1295819308686956</v>
+        <v>0.07048583185443374</v>
       </c>
     </row>
     <row r="106">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -14849,19 +14849,19 @@
         <v>48</v>
       </c>
       <c r="G118" t="n">
-        <v>3.979166666666667</v>
+        <v>4.304166666666667</v>
       </c>
       <c r="H118" t="n">
-        <v>1.02914100378605</v>
+        <v>0.7528550857514639</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1485437088924894</v>
+        <v>0.1086652716048466</v>
       </c>
       <c r="J118" t="n">
         <v>2.916666666666667</v>
       </c>
       <c r="K118" t="n">
-        <v>1.0625</v>
+        <v>1.387500000000001</v>
       </c>
     </row>
     <row r="119">
@@ -14881,7 +14881,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -14892,19 +14892,19 @@
         <v>48</v>
       </c>
       <c r="G119" t="n">
-        <v>3.995833333333334</v>
+        <v>4.095833333333333</v>
       </c>
       <c r="H119" t="n">
-        <v>1.03922195391723</v>
+        <v>1.001266927943247</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1499987687104705</v>
+        <v>0.1445204325946759</v>
       </c>
       <c r="J119" t="n">
         <v>2.904166666666667</v>
       </c>
       <c r="K119" t="n">
-        <v>1.091666666666667</v>
+        <v>1.191666666666666</v>
       </c>
     </row>
     <row r="120">
@@ -14924,7 +14924,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -14935,19 +14935,19 @@
         <v>48</v>
       </c>
       <c r="G120" t="n">
-        <v>4.083333333333333</v>
+        <v>4.304166666666667</v>
       </c>
       <c r="H120" t="n">
-        <v>0.8208281581721152</v>
+        <v>0.7528550857514639</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1184763395197739</v>
+        <v>0.1086652716048466</v>
       </c>
       <c r="J120" t="n">
         <v>2.916666666666667</v>
       </c>
       <c r="K120" t="n">
-        <v>1.166666666666667</v>
+        <v>1.387500000000001</v>
       </c>
     </row>
     <row r="121">
@@ -14967,7 +14967,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -14978,19 +14978,19 @@
         <v>48</v>
       </c>
       <c r="G121" t="n">
-        <v>4.116666666666667</v>
+        <v>4.095833333333333</v>
       </c>
       <c r="H121" t="n">
-        <v>0.8331772903548924</v>
+        <v>1.001266927943247</v>
       </c>
       <c r="I121" t="n">
-        <v>0.12025878321727</v>
+        <v>0.1445204325946759</v>
       </c>
       <c r="J121" t="n">
         <v>2.904166666666667</v>
       </c>
       <c r="K121" t="n">
-        <v>1.2125</v>
+        <v>1.191666666666666</v>
       </c>
     </row>
     <row r="122">
@@ -15526,7 +15526,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -15537,19 +15537,19 @@
         <v>48</v>
       </c>
       <c r="G134" t="n">
-        <v>4.122549019607843</v>
+        <v>4.313725490196078</v>
       </c>
       <c r="H134" t="n">
-        <v>0.7396823581240953</v>
+        <v>0.5485127882985866</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1067639521444409</v>
+        <v>0.07917100149453531</v>
       </c>
       <c r="J134" t="n">
         <v>3.026960784313725</v>
       </c>
       <c r="K134" t="n">
-        <v>1.095588235294117</v>
+        <v>1.286764705882353</v>
       </c>
     </row>
     <row r="135">
@@ -15569,7 +15569,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -15580,19 +15580,19 @@
         <v>48</v>
       </c>
       <c r="G135" t="n">
-        <v>4.068627450980392</v>
+        <v>4.202205882352941</v>
       </c>
       <c r="H135" t="n">
-        <v>0.734438383985285</v>
+        <v>0.695258629277144</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1060070496742745</v>
+        <v>0.1003519391923923</v>
       </c>
       <c r="J135" t="n">
         <v>3.004901960784314</v>
       </c>
       <c r="K135" t="n">
-        <v>1.063725490196078</v>
+        <v>1.197303921568627</v>
       </c>
     </row>
     <row r="136">
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -15623,19 +15623,19 @@
         <v>48</v>
       </c>
       <c r="G136" t="n">
-        <v>4.174019607843137</v>
+        <v>4.313725490196078</v>
       </c>
       <c r="H136" t="n">
-        <v>0.4925952967532977</v>
+        <v>0.5485127882985866</v>
       </c>
       <c r="I136" t="n">
-        <v>0.07110000679551501</v>
+        <v>0.07917100149453531</v>
       </c>
       <c r="J136" t="n">
         <v>3.026960784313725</v>
       </c>
       <c r="K136" t="n">
-        <v>1.147058823529412</v>
+        <v>1.286764705882353</v>
       </c>
     </row>
     <row r="137">
@@ -15655,7 +15655,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -15666,19 +15666,19 @@
         <v>48</v>
       </c>
       <c r="G137" t="n">
-        <v>4.105392156862745</v>
+        <v>4.202205882352941</v>
       </c>
       <c r="H137" t="n">
-        <v>0.5735280746216348</v>
+        <v>0.695258629277144</v>
       </c>
       <c r="I137" t="n">
-        <v>0.08278164706765216</v>
+        <v>0.1003519391923923</v>
       </c>
       <c r="J137" t="n">
         <v>3.004901960784314</v>
       </c>
       <c r="K137" t="n">
-        <v>1.100490196078431</v>
+        <v>1.197303921568627</v>
       </c>
     </row>
     <row r="138">

--- a/Exp3_PTO_GRPO/eda/results/arms/heterogeneity/tables/gpt-4o-mini/heterogeneity.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/heterogeneity/tables/gpt-4o-mini/heterogeneity.xlsx
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -760,19 +760,19 @@
         <v>32</v>
       </c>
       <c r="G8" t="n">
-        <v>4.854044117647059</v>
+        <v>4.939338235294118</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07414260445445435</v>
+        <v>0.0472112687345303</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01310668459614415</v>
+        <v>0.008345852067651701</v>
       </c>
       <c r="J8" t="n">
         <v>4.371875</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4821691176470591</v>
+        <v>0.5674632352941176</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -803,19 +803,19 @@
         <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>3.408639705882353</v>
+        <v>3.975367647058824</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7172720959879871</v>
+        <v>0.643530899089061</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1267969907572485</v>
+        <v>0.1137612656622377</v>
       </c>
       <c r="J9" t="n">
         <v>1.887683823529412</v>
       </c>
       <c r="K9" t="n">
-        <v>1.520955882352942</v>
+        <v>2.087683823529412</v>
       </c>
     </row>
     <row r="10">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -846,19 +846,19 @@
         <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>4.424264705882353</v>
+        <v>4.636948529411764</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2445465015192218</v>
+        <v>0.2013141021656791</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04323012238492201</v>
+        <v>0.03558764169745828</v>
       </c>
       <c r="J10" t="n">
         <v>2.629963235294118</v>
       </c>
       <c r="K10" t="n">
-        <v>1.794301470588235</v>
+        <v>2.006985294117647</v>
       </c>
     </row>
     <row r="11">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -889,19 +889,19 @@
         <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>4.854044117647059</v>
+        <v>4.939338235294118</v>
       </c>
       <c r="H11" t="n">
-        <v>0.07414260445445435</v>
+        <v>0.0472112687345303</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01310668459614415</v>
+        <v>0.008345852067651701</v>
       </c>
       <c r="J11" t="n">
         <v>4.371875</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4821691176470591</v>
+        <v>0.5674632352941176</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -932,19 +932,19 @@
         <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>3.408639705882353</v>
+        <v>3.975367647058824</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7172720959879871</v>
+        <v>0.643530899089061</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1267969907572485</v>
+        <v>0.1137612656622377</v>
       </c>
       <c r="J12" t="n">
         <v>1.887683823529412</v>
       </c>
       <c r="K12" t="n">
-        <v>1.520955882352942</v>
+        <v>2.087683823529412</v>
       </c>
     </row>
     <row r="13">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -975,19 +975,19 @@
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>4.424264705882353</v>
+        <v>4.636948529411764</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2445465015192218</v>
+        <v>0.2013141021656791</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04323012238492201</v>
+        <v>0.03558764169745828</v>
       </c>
       <c r="J13" t="n">
         <v>2.629963235294118</v>
       </c>
       <c r="K13" t="n">
-        <v>1.794301470588235</v>
+        <v>2.006985294117647</v>
       </c>
     </row>
     <row r="14">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1792,19 +1792,19 @@
         <v>32</v>
       </c>
       <c r="G32" t="n">
-        <v>4.372395833333334</v>
+        <v>4.580729166666666</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1304533984137865</v>
+        <v>0.1910689311990153</v>
       </c>
       <c r="I32" t="n">
-        <v>0.02306112066180471</v>
+        <v>0.0337765342312224</v>
       </c>
       <c r="J32" t="n">
         <v>4.15625</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2161458333333339</v>
+        <v>0.4244791666666661</v>
       </c>
     </row>
     <row r="33">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1835,19 +1835,19 @@
         <v>32</v>
       </c>
       <c r="G33" t="n">
-        <v>2.677083333333333</v>
+        <v>2.955729166666667</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4867187702260132</v>
+        <v>0.5266144212380763</v>
       </c>
       <c r="I33" t="n">
-        <v>0.08604053573939774</v>
+        <v>0.09309315708201819</v>
       </c>
       <c r="J33" t="n">
         <v>1.786458333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8906249999999998</v>
+        <v>1.169270833333333</v>
       </c>
     </row>
     <row r="34">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1878,19 +1878,19 @@
         <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>3.578125</v>
+        <v>3.651041666666667</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2783540170023813</v>
+        <v>0.2543858124523868</v>
       </c>
       <c r="I34" t="n">
-        <v>0.04920650324822484</v>
+        <v>0.044969483255683</v>
       </c>
       <c r="J34" t="n">
         <v>2.627604166666667</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9505208333333335</v>
+        <v>1.0234375</v>
       </c>
     </row>
     <row r="35">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1921,19 +1921,19 @@
         <v>32</v>
       </c>
       <c r="G35" t="n">
-        <v>4.372395833333334</v>
+        <v>4.580729166666666</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1304533984137865</v>
+        <v>0.1910689311990153</v>
       </c>
       <c r="I35" t="n">
-        <v>0.02306112066180471</v>
+        <v>0.0337765342312224</v>
       </c>
       <c r="J35" t="n">
         <v>4.15625</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2161458333333339</v>
+        <v>0.4244791666666661</v>
       </c>
     </row>
     <row r="36">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1964,19 +1964,19 @@
         <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>2.677083333333333</v>
+        <v>2.955729166666667</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4867187702260132</v>
+        <v>0.5266144212380763</v>
       </c>
       <c r="I36" t="n">
-        <v>0.08604053573939774</v>
+        <v>0.09309315708201819</v>
       </c>
       <c r="J36" t="n">
         <v>1.786458333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8906249999999998</v>
+        <v>1.169270833333333</v>
       </c>
     </row>
     <row r="37">
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2007,19 +2007,19 @@
         <v>32</v>
       </c>
       <c r="G37" t="n">
-        <v>3.578125</v>
+        <v>3.651041666666667</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2783540170023813</v>
+        <v>0.2543858124523868</v>
       </c>
       <c r="I37" t="n">
-        <v>0.04920650324822484</v>
+        <v>0.044969483255683</v>
       </c>
       <c r="J37" t="n">
         <v>2.627604166666667</v>
       </c>
       <c r="K37" t="n">
-        <v>0.9505208333333335</v>
+        <v>1.0234375</v>
       </c>
     </row>
     <row r="38">
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2867,19 +2867,19 @@
         <v>32</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>2.28125</v>
       </c>
       <c r="H57" t="n">
-        <v>0.6659942845826639</v>
+        <v>0.6245966440367219</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1177322687149712</v>
+        <v>0.1104141306261816</v>
       </c>
       <c r="J57" t="n">
         <v>1.08203125</v>
       </c>
       <c r="K57" t="n">
-        <v>0.91796875</v>
+        <v>1.19921875</v>
       </c>
     </row>
     <row r="58">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2910,19 +2910,19 @@
         <v>32</v>
       </c>
       <c r="G58" t="n">
-        <v>2.8046875</v>
+        <v>2.90625</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2374628578766956</v>
+        <v>0.3345073411605829</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0419778992711372</v>
+        <v>0.05913310232283252</v>
       </c>
       <c r="J58" t="n">
         <v>2.0703125</v>
       </c>
       <c r="K58" t="n">
-        <v>0.734375</v>
+        <v>0.8359375</v>
       </c>
     </row>
     <row r="59">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2996,19 +2996,19 @@
         <v>32</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>2.28125</v>
       </c>
       <c r="H60" t="n">
-        <v>0.6659942845826639</v>
+        <v>0.6245966440367219</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1177322687149712</v>
+        <v>0.1104141306261816</v>
       </c>
       <c r="J60" t="n">
         <v>1.08203125</v>
       </c>
       <c r="K60" t="n">
-        <v>0.91796875</v>
+        <v>1.19921875</v>
       </c>
     </row>
     <row r="61">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3039,19 +3039,19 @@
         <v>32</v>
       </c>
       <c r="G61" t="n">
-        <v>2.8046875</v>
+        <v>2.90625</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2374628578766956</v>
+        <v>0.3345073411605829</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0419778992711372</v>
+        <v>0.05913310232283252</v>
       </c>
       <c r="J61" t="n">
         <v>2.0703125</v>
       </c>
       <c r="K61" t="n">
-        <v>0.734375</v>
+        <v>0.8359375</v>
       </c>
     </row>
     <row r="62">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3856,19 +3856,19 @@
         <v>32</v>
       </c>
       <c r="G80" t="n">
-        <v>4.682291666666667</v>
+        <v>4.776041666666667</v>
       </c>
       <c r="H80" t="n">
-        <v>0.06502515366624655</v>
+        <v>0.1378884217252416</v>
       </c>
       <c r="I80" t="n">
-        <v>0.01149493177627506</v>
+        <v>0.0243754595122572</v>
       </c>
       <c r="J80" t="n">
         <v>4.541666666666667</v>
       </c>
       <c r="K80" t="n">
-        <v>0.140625</v>
+        <v>0.234375</v>
       </c>
     </row>
     <row r="81">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3899,19 +3899,19 @@
         <v>32</v>
       </c>
       <c r="G81" t="n">
-        <v>2.692708333333333</v>
+        <v>2.927083333333333</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8520577821707317</v>
+        <v>0.6785731128876609</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1506239589339236</v>
+        <v>0.1199559124134324</v>
       </c>
       <c r="J81" t="n">
         <v>1.291666666666667</v>
       </c>
       <c r="K81" t="n">
-        <v>1.401041666666666</v>
+        <v>1.635416666666666</v>
       </c>
     </row>
     <row r="82">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3942,19 +3942,19 @@
         <v>32</v>
       </c>
       <c r="G82" t="n">
-        <v>3.671875</v>
+        <v>3.791666666666667</v>
       </c>
       <c r="H82" t="n">
-        <v>0.2412793522174072</v>
+        <v>0.2609604537529376</v>
       </c>
       <c r="I82" t="n">
-        <v>0.04265256652830652</v>
+        <v>0.04613172661755514</v>
       </c>
       <c r="J82" t="n">
         <v>2.614583333333333</v>
       </c>
       <c r="K82" t="n">
-        <v>1.057291666666667</v>
+        <v>1.177083333333333</v>
       </c>
     </row>
     <row r="83">
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3985,19 +3985,19 @@
         <v>32</v>
       </c>
       <c r="G83" t="n">
-        <v>4.682291666666667</v>
+        <v>4.776041666666667</v>
       </c>
       <c r="H83" t="n">
-        <v>0.06502515366624655</v>
+        <v>0.1378884217252416</v>
       </c>
       <c r="I83" t="n">
-        <v>0.01149493177627506</v>
+        <v>0.0243754595122572</v>
       </c>
       <c r="J83" t="n">
         <v>4.541666666666667</v>
       </c>
       <c r="K83" t="n">
-        <v>0.140625</v>
+        <v>0.234375</v>
       </c>
     </row>
     <row r="84">
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4028,19 +4028,19 @@
         <v>32</v>
       </c>
       <c r="G84" t="n">
-        <v>2.692708333333333</v>
+        <v>2.927083333333333</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8520577821707317</v>
+        <v>0.6785731128876609</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1506239589339236</v>
+        <v>0.1199559124134324</v>
       </c>
       <c r="J84" t="n">
         <v>1.291666666666667</v>
       </c>
       <c r="K84" t="n">
-        <v>1.401041666666666</v>
+        <v>1.635416666666666</v>
       </c>
     </row>
     <row r="85">
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4071,19 +4071,19 @@
         <v>32</v>
       </c>
       <c r="G85" t="n">
-        <v>3.671875</v>
+        <v>3.791666666666667</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2412793522174072</v>
+        <v>0.2609604537529376</v>
       </c>
       <c r="I85" t="n">
-        <v>0.04265256652830652</v>
+        <v>0.04613172661755514</v>
       </c>
       <c r="J85" t="n">
         <v>2.614583333333333</v>
       </c>
       <c r="K85" t="n">
-        <v>1.057291666666667</v>
+        <v>1.177083333333333</v>
       </c>
     </row>
     <row r="86">
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4888,19 +4888,19 @@
         <v>32</v>
       </c>
       <c r="G104" t="n">
-        <v>4.578125</v>
+        <v>4.828125</v>
       </c>
       <c r="H104" t="n">
-        <v>0.249495458617923</v>
+        <v>0.2412793522174071</v>
       </c>
       <c r="I104" t="n">
-        <v>0.04410498266599525</v>
+        <v>0.04265256652830651</v>
       </c>
       <c r="J104" t="n">
         <v>4.1640625</v>
       </c>
       <c r="K104" t="n">
-        <v>0.4140625</v>
+        <v>0.6640625</v>
       </c>
     </row>
     <row r="105">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4931,19 +4931,19 @@
         <v>32</v>
       </c>
       <c r="G105" t="n">
-        <v>3.6640625</v>
+        <v>4.03125</v>
       </c>
       <c r="H105" t="n">
-        <v>0.587536460776636</v>
+        <v>0.5563054974127192</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1038627539023758</v>
+        <v>0.09834184740797226</v>
       </c>
       <c r="J105" t="n">
         <v>2.234375</v>
       </c>
       <c r="K105" t="n">
-        <v>1.4296875</v>
+        <v>1.796875</v>
       </c>
     </row>
     <row r="106">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4974,19 +4974,19 @@
         <v>32</v>
       </c>
       <c r="G106" t="n">
-        <v>4.5078125</v>
+        <v>4.75</v>
       </c>
       <c r="H106" t="n">
-        <v>0.2802963221767393</v>
+        <v>0.2459346884189824</v>
       </c>
       <c r="I106" t="n">
-        <v>0.04954985753820541</v>
+        <v>0.04347552147751577</v>
       </c>
       <c r="J106" t="n">
         <v>2.9609375</v>
       </c>
       <c r="K106" t="n">
-        <v>1.546875</v>
+        <v>1.7890625</v>
       </c>
     </row>
     <row r="107">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -5017,19 +5017,19 @@
         <v>32</v>
       </c>
       <c r="G107" t="n">
-        <v>4.578125</v>
+        <v>4.828125</v>
       </c>
       <c r="H107" t="n">
-        <v>0.249495458617923</v>
+        <v>0.2412793522174071</v>
       </c>
       <c r="I107" t="n">
-        <v>0.04410498266599525</v>
+        <v>0.04265256652830651</v>
       </c>
       <c r="J107" t="n">
         <v>4.1640625</v>
       </c>
       <c r="K107" t="n">
-        <v>0.4140625</v>
+        <v>0.6640625</v>
       </c>
     </row>
     <row r="108">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5060,19 +5060,19 @@
         <v>32</v>
       </c>
       <c r="G108" t="n">
-        <v>3.6640625</v>
+        <v>4.03125</v>
       </c>
       <c r="H108" t="n">
-        <v>0.587536460776636</v>
+        <v>0.5563054974127192</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1038627539023758</v>
+        <v>0.09834184740797226</v>
       </c>
       <c r="J108" t="n">
         <v>2.234375</v>
       </c>
       <c r="K108" t="n">
-        <v>1.4296875</v>
+        <v>1.796875</v>
       </c>
     </row>
     <row r="109">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -5103,19 +5103,19 @@
         <v>32</v>
       </c>
       <c r="G109" t="n">
-        <v>4.5078125</v>
+        <v>4.75</v>
       </c>
       <c r="H109" t="n">
-        <v>0.2802963221767393</v>
+        <v>0.2459346884189824</v>
       </c>
       <c r="I109" t="n">
-        <v>0.04954985753820541</v>
+        <v>0.04347552147751577</v>
       </c>
       <c r="J109" t="n">
         <v>2.9609375</v>
       </c>
       <c r="K109" t="n">
-        <v>1.546875</v>
+        <v>1.7890625</v>
       </c>
     </row>
     <row r="110">
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5920,19 +5920,19 @@
         <v>32</v>
       </c>
       <c r="G128" t="n">
-        <v>0.8569006099576753</v>
+        <v>0.8787868004579962</v>
       </c>
       <c r="H128" t="n">
-        <v>0.05900058772222223</v>
+        <v>0.07333511798695803</v>
       </c>
       <c r="I128" t="n">
-        <v>0.01042992891809377</v>
+        <v>0.01296393980692339</v>
       </c>
       <c r="J128" t="n">
         <v>0.8269659801249475</v>
       </c>
       <c r="K128" t="n">
-        <v>0.02993462983272777</v>
+        <v>0.05182082033304869</v>
       </c>
     </row>
     <row r="129">
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5963,19 +5963,19 @@
         <v>32</v>
       </c>
       <c r="G129" t="n">
-        <v>0.3619417686693102</v>
+        <v>0.4672090079874396</v>
       </c>
       <c r="H129" t="n">
-        <v>0.2396955014699558</v>
+        <v>0.2053759460907271</v>
       </c>
       <c r="I129" t="n">
-        <v>0.04237257862732895</v>
+        <v>0.03630568104333899</v>
       </c>
       <c r="J129" t="n">
         <v>0.14071079687856</v>
       </c>
       <c r="K129" t="n">
-        <v>0.2212309717907502</v>
+        <v>0.3264982111088796</v>
       </c>
     </row>
     <row r="130">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -6006,19 +6006,19 @@
         <v>32</v>
       </c>
       <c r="G130" t="n">
-        <v>0.656460424185303</v>
+        <v>0.7093175845893237</v>
       </c>
       <c r="H130" t="n">
-        <v>0.07324949339596523</v>
+        <v>0.08896178340704643</v>
       </c>
       <c r="I130" t="n">
-        <v>0.01294880337469156</v>
+        <v>0.01572637007839285</v>
       </c>
       <c r="J130" t="n">
         <v>0.4445382507163197</v>
       </c>
       <c r="K130" t="n">
-        <v>0.2119221734689833</v>
+        <v>0.264779333873004</v>
       </c>
     </row>
     <row r="131">
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -6049,19 +6049,19 @@
         <v>32</v>
       </c>
       <c r="G131" t="n">
-        <v>0.8569006099576753</v>
+        <v>0.8787868004579962</v>
       </c>
       <c r="H131" t="n">
-        <v>0.05900058772222223</v>
+        <v>0.07333511798695803</v>
       </c>
       <c r="I131" t="n">
-        <v>0.01042992891809377</v>
+        <v>0.01296393980692339</v>
       </c>
       <c r="J131" t="n">
         <v>0.8269659801249475</v>
       </c>
       <c r="K131" t="n">
-        <v>0.02993462983272777</v>
+        <v>0.05182082033304869</v>
       </c>
     </row>
     <row r="132">
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -6092,19 +6092,19 @@
         <v>32</v>
       </c>
       <c r="G132" t="n">
-        <v>0.3619417686693102</v>
+        <v>0.4672090079874396</v>
       </c>
       <c r="H132" t="n">
-        <v>0.2396955014699558</v>
+        <v>0.2053759460907271</v>
       </c>
       <c r="I132" t="n">
-        <v>0.04237257862732895</v>
+        <v>0.03630568104333899</v>
       </c>
       <c r="J132" t="n">
         <v>0.14071079687856</v>
       </c>
       <c r="K132" t="n">
-        <v>0.2212309717907502</v>
+        <v>0.3264982111088796</v>
       </c>
     </row>
     <row r="133">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -6135,19 +6135,19 @@
         <v>32</v>
       </c>
       <c r="G133" t="n">
-        <v>0.656460424185303</v>
+        <v>0.7093175845893237</v>
       </c>
       <c r="H133" t="n">
-        <v>0.07324949339596523</v>
+        <v>0.08896178340704643</v>
       </c>
       <c r="I133" t="n">
-        <v>0.01294880337469156</v>
+        <v>0.01572637007839285</v>
       </c>
       <c r="J133" t="n">
         <v>0.4445382507163197</v>
       </c>
       <c r="K133" t="n">
-        <v>0.2119221734689833</v>
+        <v>0.264779333873004</v>
       </c>
     </row>
     <row r="134">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -6952,19 +6952,19 @@
         <v>32</v>
       </c>
       <c r="G152" t="n">
-        <v>0.2788451479076479</v>
+        <v>0.2044602793040293</v>
       </c>
       <c r="H152" t="n">
-        <v>0.1458108650348325</v>
+        <v>0.1684481809920274</v>
       </c>
       <c r="I152" t="n">
-        <v>0.02577596285920162</v>
+        <v>0.02977771276450036</v>
       </c>
       <c r="J152" t="n">
         <v>0.2408584731240981</v>
       </c>
       <c r="K152" t="n">
-        <v>0.03798667478354975</v>
+        <v>-0.03639819382006881</v>
       </c>
     </row>
     <row r="153">
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -6995,19 +6995,19 @@
         <v>32</v>
       </c>
       <c r="G153" t="n">
-        <v>0.2641779906432576</v>
+        <v>0.2360338171084591</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1372888643130128</v>
+        <v>0.1076940893623445</v>
       </c>
       <c r="I153" t="n">
-        <v>0.02426947173428279</v>
+        <v>0.01903780522045595</v>
       </c>
       <c r="J153" t="n">
         <v>0.2097223436285936</v>
       </c>
       <c r="K153" t="n">
-        <v>0.05445564701466402</v>
+        <v>0.02631147347986548</v>
       </c>
     </row>
     <row r="154">
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -7038,19 +7038,19 @@
         <v>32</v>
       </c>
       <c r="G154" t="n">
-        <v>0.3008668097809259</v>
+        <v>0.1909962346681097</v>
       </c>
       <c r="H154" t="n">
-        <v>0.1757768738896749</v>
+        <v>0.1080799855295258</v>
       </c>
       <c r="I154" t="n">
-        <v>0.03107325487579043</v>
+        <v>0.01910602266961791</v>
       </c>
       <c r="J154" t="n">
         <v>0.1764841321872572</v>
       </c>
       <c r="K154" t="n">
-        <v>0.1243826775936687</v>
+        <v>0.0145121024808525</v>
       </c>
     </row>
     <row r="155">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -7081,19 +7081,19 @@
         <v>32</v>
       </c>
       <c r="G155" t="n">
-        <v>0.2788451479076479</v>
+        <v>0.2044602793040293</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1458108650348325</v>
+        <v>0.1684481809920274</v>
       </c>
       <c r="I155" t="n">
-        <v>0.02577596285920162</v>
+        <v>0.02977771276450036</v>
       </c>
       <c r="J155" t="n">
         <v>0.2408584731240981</v>
       </c>
       <c r="K155" t="n">
-        <v>0.03798667478354975</v>
+        <v>-0.03639819382006881</v>
       </c>
     </row>
     <row r="156">
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -7124,19 +7124,19 @@
         <v>32</v>
       </c>
       <c r="G156" t="n">
-        <v>0.2641779906432576</v>
+        <v>0.2360338171084591</v>
       </c>
       <c r="H156" t="n">
-        <v>0.1372888643130128</v>
+        <v>0.1076940893623445</v>
       </c>
       <c r="I156" t="n">
-        <v>0.02426947173428279</v>
+        <v>0.01903780522045595</v>
       </c>
       <c r="J156" t="n">
         <v>0.2097223436285936</v>
       </c>
       <c r="K156" t="n">
-        <v>0.05445564701466402</v>
+        <v>0.02631147347986548</v>
       </c>
     </row>
     <row r="157">
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -7167,19 +7167,19 @@
         <v>32</v>
       </c>
       <c r="G157" t="n">
-        <v>0.3008668097809259</v>
+        <v>0.1909962346681097</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1757768738896749</v>
+        <v>0.1080799855295258</v>
       </c>
       <c r="I157" t="n">
-        <v>0.03107325487579043</v>
+        <v>0.01910602266961791</v>
       </c>
       <c r="J157" t="n">
         <v>0.1764841321872572</v>
       </c>
       <c r="K157" t="n">
-        <v>0.1243826775936687</v>
+        <v>0.0145121024808525</v>
       </c>
     </row>
     <row r="158">
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -7984,19 +7984,19 @@
         <v>32</v>
       </c>
       <c r="G176" t="n">
-        <v>4.9875</v>
+        <v>5</v>
       </c>
       <c r="H176" t="n">
-        <v>0.07071067811865481</v>
+        <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>0.01250000000000001</v>
+        <v>0</v>
       </c>
       <c r="J176" t="n">
         <v>4.4625</v>
       </c>
       <c r="K176" t="n">
-        <v>0.5249999999999995</v>
+        <v>0.5374999999999996</v>
       </c>
     </row>
     <row r="177">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -8027,19 +8027,19 @@
         <v>32</v>
       </c>
       <c r="G177" t="n">
-        <v>3.2125</v>
+        <v>3.76875</v>
       </c>
       <c r="H177" t="n">
-        <v>0.801510670445946</v>
+        <v>0.7953240362145766</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1416884075664261</v>
+        <v>0.1405947548119956</v>
       </c>
       <c r="J177" t="n">
         <v>1.7</v>
       </c>
       <c r="K177" t="n">
-        <v>1.5125</v>
+        <v>2.06875</v>
       </c>
     </row>
     <row r="178">
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -8070,19 +8070,19 @@
         <v>32</v>
       </c>
       <c r="G178" t="n">
-        <v>4.4</v>
+        <v>4.625</v>
       </c>
       <c r="H178" t="n">
-        <v>0.2782433374561009</v>
+        <v>0.2257603639602926</v>
       </c>
       <c r="I178" t="n">
-        <v>0.04918693768379645</v>
+        <v>0.03990917106986649</v>
       </c>
       <c r="J178" t="n">
         <v>2.56875</v>
       </c>
       <c r="K178" t="n">
-        <v>1.83125</v>
+        <v>2.05625</v>
       </c>
     </row>
     <row r="179">
@@ -8102,7 +8102,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -8113,19 +8113,19 @@
         <v>32</v>
       </c>
       <c r="G179" t="n">
-        <v>4.9875</v>
+        <v>5</v>
       </c>
       <c r="H179" t="n">
-        <v>0.07071067811865481</v>
+        <v>0</v>
       </c>
       <c r="I179" t="n">
-        <v>0.01250000000000001</v>
+        <v>0</v>
       </c>
       <c r="J179" t="n">
         <v>4.4625</v>
       </c>
       <c r="K179" t="n">
-        <v>0.5249999999999995</v>
+        <v>0.5374999999999996</v>
       </c>
     </row>
     <row r="180">
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -8156,19 +8156,19 @@
         <v>32</v>
       </c>
       <c r="G180" t="n">
-        <v>3.2125</v>
+        <v>3.76875</v>
       </c>
       <c r="H180" t="n">
-        <v>0.801510670445946</v>
+        <v>0.7953240362145766</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1416884075664261</v>
+        <v>0.1405947548119956</v>
       </c>
       <c r="J180" t="n">
         <v>1.7</v>
       </c>
       <c r="K180" t="n">
-        <v>1.5125</v>
+        <v>2.06875</v>
       </c>
     </row>
     <row r="181">
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -8199,19 +8199,19 @@
         <v>32</v>
       </c>
       <c r="G181" t="n">
-        <v>4.4</v>
+        <v>4.625</v>
       </c>
       <c r="H181" t="n">
-        <v>0.2782433374561009</v>
+        <v>0.2257603639602926</v>
       </c>
       <c r="I181" t="n">
-        <v>0.04918693768379645</v>
+        <v>0.03990917106986649</v>
       </c>
       <c r="J181" t="n">
         <v>2.56875</v>
       </c>
       <c r="K181" t="n">
-        <v>1.83125</v>
+        <v>2.05625</v>
       </c>
     </row>
     <row r="182">
@@ -9005,7 +9005,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -9016,19 +9016,19 @@
         <v>32</v>
       </c>
       <c r="G200" t="n">
-        <v>4.720588235294118</v>
+        <v>4.878676470588236</v>
       </c>
       <c r="H200" t="n">
-        <v>0.1097948853243979</v>
+        <v>0.094422537469061</v>
       </c>
       <c r="I200" t="n">
-        <v>0.01940917698812028</v>
+        <v>0.01669170413530347</v>
       </c>
       <c r="J200" t="n">
         <v>4.28125</v>
       </c>
       <c r="K200" t="n">
-        <v>0.4393382352941178</v>
+        <v>0.5974264705882355</v>
       </c>
     </row>
     <row r="201">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -9059,19 +9059,19 @@
         <v>32</v>
       </c>
       <c r="G201" t="n">
-        <v>3.604779411764706</v>
+        <v>4.181985294117647</v>
       </c>
       <c r="H201" t="n">
-        <v>0.66033209891481</v>
+        <v>0.521736343728757</v>
       </c>
       <c r="I201" t="n">
-        <v>0.1167313262444521</v>
+        <v>0.09223082666051988</v>
       </c>
       <c r="J201" t="n">
         <v>2.075367647058823</v>
       </c>
       <c r="K201" t="n">
-        <v>1.529411764705882</v>
+        <v>2.106617647058823</v>
       </c>
     </row>
     <row r="202">
@@ -9091,7 +9091,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -9102,19 +9102,19 @@
         <v>32</v>
       </c>
       <c r="G202" t="n">
-        <v>4.448529411764706</v>
+        <v>4.648897058823529</v>
       </c>
       <c r="H202" t="n">
-        <v>0.2274547972372718</v>
+        <v>0.1939389523094944</v>
       </c>
       <c r="I202" t="n">
-        <v>0.04020870738497152</v>
+        <v>0.03428388707856447</v>
       </c>
       <c r="J202" t="n">
         <v>2.691176470588236</v>
       </c>
       <c r="K202" t="n">
-        <v>1.75735294117647</v>
+        <v>1.957720588235293</v>
       </c>
     </row>
     <row r="203">
@@ -9134,7 +9134,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -9145,19 +9145,19 @@
         <v>32</v>
       </c>
       <c r="G203" t="n">
-        <v>4.720588235294118</v>
+        <v>4.878676470588236</v>
       </c>
       <c r="H203" t="n">
-        <v>0.1097948853243979</v>
+        <v>0.094422537469061</v>
       </c>
       <c r="I203" t="n">
-        <v>0.01940917698812028</v>
+        <v>0.01669170413530347</v>
       </c>
       <c r="J203" t="n">
         <v>4.28125</v>
       </c>
       <c r="K203" t="n">
-        <v>0.4393382352941178</v>
+        <v>0.5974264705882355</v>
       </c>
     </row>
     <row r="204">
@@ -9177,7 +9177,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -9188,19 +9188,19 @@
         <v>32</v>
       </c>
       <c r="G204" t="n">
-        <v>3.604779411764706</v>
+        <v>4.181985294117647</v>
       </c>
       <c r="H204" t="n">
-        <v>0.66033209891481</v>
+        <v>0.521736343728757</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1167313262444521</v>
+        <v>0.09223082666051988</v>
       </c>
       <c r="J204" t="n">
         <v>2.075367647058823</v>
       </c>
       <c r="K204" t="n">
-        <v>1.529411764705882</v>
+        <v>2.106617647058823</v>
       </c>
     </row>
     <row r="205">
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -9231,19 +9231,19 @@
         <v>32</v>
       </c>
       <c r="G205" t="n">
-        <v>4.448529411764706</v>
+        <v>4.648897058823529</v>
       </c>
       <c r="H205" t="n">
-        <v>0.2274547972372718</v>
+        <v>0.1939389523094944</v>
       </c>
       <c r="I205" t="n">
-        <v>0.04020870738497152</v>
+        <v>0.03428388707856447</v>
       </c>
       <c r="J205" t="n">
         <v>2.691176470588236</v>
       </c>
       <c r="K205" t="n">
-        <v>1.75735294117647</v>
+        <v>1.957720588235293</v>
       </c>
     </row>
     <row r="206">
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -10033,19 +10033,19 @@
         <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>4.308946078431373</v>
+        <v>4.543259803921568</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6423528833928527</v>
+        <v>0.4102448072312048</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09271565253539896</v>
+        <v>0.05921373747214555</v>
       </c>
       <c r="J6" t="n">
         <v>2.971813725490196</v>
       </c>
       <c r="K6" t="n">
-        <v>1.337132352941177</v>
+        <v>1.571446078431372</v>
       </c>
     </row>
     <row r="7">
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -10076,19 +10076,19 @@
         <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>4.149019607843138</v>
+        <v>4.491176470588235</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8407683732509679</v>
+        <v>0.6801786600918971</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1213544616556425</v>
+        <v>0.09817533312527395</v>
       </c>
       <c r="J7" t="n">
         <v>2.95453431372549</v>
       </c>
       <c r="K7" t="n">
-        <v>1.194485294117647</v>
+        <v>1.536642156862745</v>
       </c>
     </row>
     <row r="8">
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -10119,19 +10119,19 @@
         <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>4.308946078431373</v>
+        <v>4.543259803921568</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6423528833928527</v>
+        <v>0.4102448072312048</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09271565253539896</v>
+        <v>0.05921373747214555</v>
       </c>
       <c r="J8" t="n">
         <v>2.971813725490196</v>
       </c>
       <c r="K8" t="n">
-        <v>1.337132352941177</v>
+        <v>1.571446078431372</v>
       </c>
     </row>
     <row r="9">
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -10162,19 +10162,19 @@
         <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>4.149019607843138</v>
+        <v>4.491176470588235</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8407683732509679</v>
+        <v>0.6801786600918971</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1213544616556425</v>
+        <v>0.09817533312527395</v>
       </c>
       <c r="J9" t="n">
         <v>2.95453431372549</v>
       </c>
       <c r="K9" t="n">
-        <v>1.194485294117647</v>
+        <v>1.536642156862745</v>
       </c>
     </row>
     <row r="10">
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -10721,19 +10721,19 @@
         <v>48</v>
       </c>
       <c r="G22" t="n">
-        <v>3.600694444444444</v>
+        <v>3.715277777777777</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7211672828151556</v>
+        <v>0.750459538753783</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1040915312160203</v>
+        <v>0.1083195041788548</v>
       </c>
       <c r="J22" t="n">
         <v>2.828125</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7725694444444442</v>
+        <v>0.8871527777777772</v>
       </c>
     </row>
     <row r="23">
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -10764,19 +10764,19 @@
         <v>48</v>
       </c>
       <c r="G23" t="n">
-        <v>3.484375</v>
+        <v>3.743055555555556</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8193248550392612</v>
+        <v>0.7689361516787659</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1182593564026671</v>
+        <v>0.1109863735403426</v>
       </c>
       <c r="J23" t="n">
         <v>2.885416666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5989583333333335</v>
+        <v>0.8576388888888893</v>
       </c>
     </row>
     <row r="24">
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -10807,19 +10807,19 @@
         <v>48</v>
       </c>
       <c r="G24" t="n">
-        <v>3.600694444444444</v>
+        <v>3.715277777777777</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7211672828151556</v>
+        <v>0.750459538753783</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1040915312160203</v>
+        <v>0.1083195041788548</v>
       </c>
       <c r="J24" t="n">
         <v>2.828125</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7725694444444442</v>
+        <v>0.8871527777777772</v>
       </c>
     </row>
     <row r="25">
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -10850,19 +10850,19 @@
         <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>3.484375</v>
+        <v>3.743055555555556</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8193248550392612</v>
+        <v>0.7689361516787659</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1182593564026671</v>
+        <v>0.1109863735403426</v>
       </c>
       <c r="J25" t="n">
         <v>2.885416666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5989583333333335</v>
+        <v>0.8576388888888893</v>
       </c>
     </row>
     <row r="26">
@@ -11398,7 +11398,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -11409,19 +11409,19 @@
         <v>48</v>
       </c>
       <c r="G38" t="n">
-        <v>3.005208333333333</v>
+        <v>3.0546875</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8454187923137049</v>
+        <v>0.7892673725502279</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1220256918300715</v>
+        <v>0.1139209325011157</v>
       </c>
       <c r="J38" t="n">
         <v>2.317708333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6875</v>
+        <v>0.7369791666666665</v>
       </c>
     </row>
     <row r="39">
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -11452,19 +11452,19 @@
         <v>48</v>
       </c>
       <c r="G39" t="n">
-        <v>2.864583333333333</v>
+        <v>3.0703125</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9919333332380017</v>
+        <v>0.8594384647745541</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1431732442407808</v>
+        <v>0.1240492572473769</v>
       </c>
       <c r="J39" t="n">
         <v>2.393229166666667</v>
       </c>
       <c r="K39" t="n">
-        <v>0.471354166666667</v>
+        <v>0.6770833333333335</v>
       </c>
     </row>
     <row r="40">
@@ -11484,7 +11484,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -11495,19 +11495,19 @@
         <v>48</v>
       </c>
       <c r="G40" t="n">
-        <v>3.005208333333333</v>
+        <v>3.0546875</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8454187923137049</v>
+        <v>0.7892673725502279</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1220256918300715</v>
+        <v>0.1139209325011157</v>
       </c>
       <c r="J40" t="n">
         <v>2.317708333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6875</v>
+        <v>0.7369791666666665</v>
       </c>
     </row>
     <row r="41">
@@ -11527,7 +11527,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -11538,19 +11538,19 @@
         <v>48</v>
       </c>
       <c r="G41" t="n">
-        <v>2.864583333333333</v>
+        <v>3.0703125</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9919333332380017</v>
+        <v>0.8594384647745541</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1431732442407808</v>
+        <v>0.1240492572473769</v>
       </c>
       <c r="J41" t="n">
         <v>2.393229166666667</v>
       </c>
       <c r="K41" t="n">
-        <v>0.471354166666667</v>
+        <v>0.6770833333333335</v>
       </c>
     </row>
     <row r="42">
@@ -12086,7 +12086,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -12097,19 +12097,19 @@
         <v>48</v>
       </c>
       <c r="G54" t="n">
-        <v>3.78125</v>
+        <v>3.836805555555556</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8840297335157641</v>
+        <v>0.8124981057139826</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1275987011542399</v>
+        <v>0.1172740000125072</v>
       </c>
       <c r="J54" t="n">
         <v>2.784722222222222</v>
       </c>
       <c r="K54" t="n">
-        <v>0.9965277777777781</v>
+        <v>1.052083333333334</v>
       </c>
     </row>
     <row r="55">
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -12140,19 +12140,19 @@
         <v>48</v>
       </c>
       <c r="G55" t="n">
-        <v>3.583333333333333</v>
+        <v>3.826388888888889</v>
       </c>
       <c r="H55" t="n">
-        <v>1.032566633892407</v>
+        <v>0.930795900650751</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1490381560085018</v>
+        <v>0.1343488159503278</v>
       </c>
       <c r="J55" t="n">
         <v>2.847222222222222</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7361111111111116</v>
+        <v>0.979166666666667</v>
       </c>
     </row>
     <row r="56">
@@ -12172,7 +12172,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -12183,19 +12183,19 @@
         <v>48</v>
       </c>
       <c r="G56" t="n">
-        <v>3.78125</v>
+        <v>3.836805555555556</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8840297335157641</v>
+        <v>0.8124981057139826</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1275987011542399</v>
+        <v>0.1172740000125072</v>
       </c>
       <c r="J56" t="n">
         <v>2.784722222222222</v>
       </c>
       <c r="K56" t="n">
-        <v>0.9965277777777781</v>
+        <v>1.052083333333334</v>
       </c>
     </row>
     <row r="57">
@@ -12215,7 +12215,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -12226,19 +12226,19 @@
         <v>48</v>
       </c>
       <c r="G57" t="n">
-        <v>3.583333333333333</v>
+        <v>3.826388888888889</v>
       </c>
       <c r="H57" t="n">
-        <v>1.032566633892407</v>
+        <v>0.930795900650751</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1490381560085018</v>
+        <v>0.1343488159503278</v>
       </c>
       <c r="J57" t="n">
         <v>2.847222222222222</v>
       </c>
       <c r="K57" t="n">
-        <v>0.7361111111111116</v>
+        <v>0.979166666666667</v>
       </c>
     </row>
     <row r="58">
@@ -12774,7 +12774,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -12785,19 +12785,19 @@
         <v>48</v>
       </c>
       <c r="G70" t="n">
-        <v>4.317708333333333</v>
+        <v>4.546875</v>
       </c>
       <c r="H70" t="n">
-        <v>0.4633928510423559</v>
+        <v>0.4114590346973105</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0668849968224631</v>
+        <v>0.05938899611074895</v>
       </c>
       <c r="J70" t="n">
         <v>3.114583333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>1.203125</v>
+        <v>1.432291666666667</v>
       </c>
     </row>
     <row r="71">
@@ -12817,7 +12817,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -12828,19 +12828,19 @@
         <v>48</v>
       </c>
       <c r="G71" t="n">
-        <v>4.182291666666667</v>
+        <v>4.526041666666667</v>
       </c>
       <c r="H71" t="n">
-        <v>0.6699070738458077</v>
+        <v>0.6128924781038775</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0966927573542279</v>
+        <v>0.08846340930439263</v>
       </c>
       <c r="J71" t="n">
         <v>3.125</v>
       </c>
       <c r="K71" t="n">
-        <v>1.057291666666667</v>
+        <v>1.401041666666667</v>
       </c>
     </row>
     <row r="72">
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -12871,19 +12871,19 @@
         <v>48</v>
       </c>
       <c r="G72" t="n">
-        <v>4.317708333333333</v>
+        <v>4.546875</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4633928510423559</v>
+        <v>0.4114590346973105</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0668849968224631</v>
+        <v>0.05938899611074895</v>
       </c>
       <c r="J72" t="n">
         <v>3.114583333333333</v>
       </c>
       <c r="K72" t="n">
-        <v>1.203125</v>
+        <v>1.432291666666667</v>
       </c>
     </row>
     <row r="73">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -12914,19 +12914,19 @@
         <v>48</v>
       </c>
       <c r="G73" t="n">
-        <v>4.182291666666667</v>
+        <v>4.526041666666667</v>
       </c>
       <c r="H73" t="n">
-        <v>0.6699070738458077</v>
+        <v>0.6128924781038775</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0966927573542279</v>
+        <v>0.08846340930439263</v>
       </c>
       <c r="J73" t="n">
         <v>3.125</v>
       </c>
       <c r="K73" t="n">
-        <v>1.057291666666667</v>
+        <v>1.401041666666667</v>
       </c>
     </row>
     <row r="74">
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -13473,19 +13473,19 @@
         <v>48</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6445138674198777</v>
+        <v>0.6746614014596751</v>
       </c>
       <c r="H86" t="n">
-        <v>0.229354465554107</v>
+        <v>0.1928325308905648</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0331044656068766</v>
+        <v>0.02783297840454611</v>
       </c>
       <c r="J86" t="n">
         <v>0.464800525657892</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1797133417619857</v>
+        <v>0.2098608758017831</v>
       </c>
     </row>
     <row r="87">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -13516,19 +13516,19 @@
         <v>48</v>
       </c>
       <c r="G87" t="n">
-        <v>0.605688001121648</v>
+        <v>0.6955475272301644</v>
       </c>
       <c r="H87" t="n">
-        <v>0.2734229620700355</v>
+        <v>0.2396790010014723</v>
       </c>
       <c r="I87" t="n">
-        <v>0.03946520518843995</v>
+        <v>0.03459468393682515</v>
       </c>
       <c r="J87" t="n">
         <v>0.4766761594886595</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1290118416329885</v>
+        <v>0.218871367741505</v>
       </c>
     </row>
     <row r="88">
@@ -13548,7 +13548,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -13559,19 +13559,19 @@
         <v>48</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6445138674198777</v>
+        <v>0.6746614014596751</v>
       </c>
       <c r="H88" t="n">
-        <v>0.229354465554107</v>
+        <v>0.1928325308905648</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0331044656068766</v>
+        <v>0.02783297840454611</v>
       </c>
       <c r="J88" t="n">
         <v>0.464800525657892</v>
       </c>
       <c r="K88" t="n">
-        <v>0.1797133417619857</v>
+        <v>0.2098608758017831</v>
       </c>
     </row>
     <row r="89">
@@ -13591,7 +13591,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -13602,19 +13602,19 @@
         <v>48</v>
       </c>
       <c r="G89" t="n">
-        <v>0.605688001121648</v>
+        <v>0.6955475272301644</v>
       </c>
       <c r="H89" t="n">
-        <v>0.2734229620700355</v>
+        <v>0.2396790010014723</v>
       </c>
       <c r="I89" t="n">
-        <v>0.03946520518843995</v>
+        <v>0.03459468393682515</v>
       </c>
       <c r="J89" t="n">
         <v>0.4766761594886595</v>
       </c>
       <c r="K89" t="n">
-        <v>0.1290118416329885</v>
+        <v>0.218871367741505</v>
       </c>
     </row>
     <row r="90">
@@ -14150,7 +14150,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -14161,19 +14161,19 @@
         <v>48</v>
       </c>
       <c r="G102" t="n">
-        <v>0.2764341183913552</v>
+        <v>0.2021190026791807</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1384857643827544</v>
+        <v>0.128570387625918</v>
       </c>
       <c r="I102" t="n">
-        <v>0.01998869833632858</v>
+        <v>0.01855753697640958</v>
       </c>
       <c r="J102" t="n">
         <v>0.2023699506512006</v>
       </c>
       <c r="K102" t="n">
-        <v>0.07406416774015459</v>
+        <v>-0.0002509479720199659</v>
       </c>
     </row>
     <row r="103">
@@ -14193,7 +14193,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -14204,19 +14204,19 @@
         <v>48</v>
       </c>
       <c r="G103" t="n">
-        <v>0.2861591804965324</v>
+        <v>0.2188745513745514</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1675466505440653</v>
+        <v>0.1346244465762891</v>
       </c>
       <c r="I103" t="n">
-        <v>0.02418327594835907</v>
+        <v>0.01943136511758122</v>
       </c>
       <c r="J103" t="n">
         <v>0.2156733486420986</v>
       </c>
       <c r="K103" t="n">
-        <v>0.07048583185443374</v>
+        <v>0.003201202732452724</v>
       </c>
     </row>
     <row r="104">
@@ -14236,7 +14236,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -14247,19 +14247,19 @@
         <v>48</v>
       </c>
       <c r="G104" t="n">
-        <v>0.2764341183913552</v>
+        <v>0.2021190026791807</v>
       </c>
       <c r="H104" t="n">
-        <v>0.1384857643827544</v>
+        <v>0.128570387625918</v>
       </c>
       <c r="I104" t="n">
-        <v>0.01998869833632858</v>
+        <v>0.01855753697640958</v>
       </c>
       <c r="J104" t="n">
         <v>0.2023699506512006</v>
       </c>
       <c r="K104" t="n">
-        <v>0.07406416774015459</v>
+        <v>-0.0002509479720199659</v>
       </c>
     </row>
     <row r="105">
@@ -14279,7 +14279,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -14290,19 +14290,19 @@
         <v>48</v>
       </c>
       <c r="G105" t="n">
-        <v>0.2861591804965324</v>
+        <v>0.2188745513745514</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1675466505440653</v>
+        <v>0.1346244465762891</v>
       </c>
       <c r="I105" t="n">
-        <v>0.02418327594835907</v>
+        <v>0.01943136511758122</v>
       </c>
       <c r="J105" t="n">
         <v>0.2156733486420986</v>
       </c>
       <c r="K105" t="n">
-        <v>0.07048583185443374</v>
+        <v>0.003201202732452724</v>
       </c>
     </row>
     <row r="106">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -14849,19 +14849,19 @@
         <v>48</v>
       </c>
       <c r="G118" t="n">
-        <v>4.304166666666667</v>
+        <v>4.495833333333333</v>
       </c>
       <c r="H118" t="n">
-        <v>0.7528550857514639</v>
+        <v>0.5504189249179223</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1086652716048466</v>
+        <v>0.07944612861710672</v>
       </c>
       <c r="J118" t="n">
         <v>2.916666666666667</v>
       </c>
       <c r="K118" t="n">
-        <v>1.387500000000001</v>
+        <v>1.579166666666666</v>
       </c>
     </row>
     <row r="119">
@@ -14881,7 +14881,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -14892,19 +14892,19 @@
         <v>48</v>
       </c>
       <c r="G119" t="n">
-        <v>4.095833333333333</v>
+        <v>4.433333333333333</v>
       </c>
       <c r="H119" t="n">
-        <v>1.001266927943247</v>
+        <v>0.8295944493272661</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1445204325946759</v>
+        <v>0.1197416446593291</v>
       </c>
       <c r="J119" t="n">
         <v>2.904166666666667</v>
       </c>
       <c r="K119" t="n">
-        <v>1.191666666666666</v>
+        <v>1.529166666666666</v>
       </c>
     </row>
     <row r="120">
@@ -14924,7 +14924,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -14935,19 +14935,19 @@
         <v>48</v>
       </c>
       <c r="G120" t="n">
-        <v>4.304166666666667</v>
+        <v>4.495833333333333</v>
       </c>
       <c r="H120" t="n">
-        <v>0.7528550857514639</v>
+        <v>0.5504189249179223</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1086652716048466</v>
+        <v>0.07944612861710672</v>
       </c>
       <c r="J120" t="n">
         <v>2.916666666666667</v>
       </c>
       <c r="K120" t="n">
-        <v>1.387500000000001</v>
+        <v>1.579166666666666</v>
       </c>
     </row>
     <row r="121">
@@ -14967,7 +14967,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -14978,19 +14978,19 @@
         <v>48</v>
       </c>
       <c r="G121" t="n">
-        <v>4.095833333333333</v>
+        <v>4.433333333333333</v>
       </c>
       <c r="H121" t="n">
-        <v>1.001266927943247</v>
+        <v>0.8295944493272661</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1445204325946759</v>
+        <v>0.1197416446593291</v>
       </c>
       <c r="J121" t="n">
         <v>2.904166666666667</v>
       </c>
       <c r="K121" t="n">
-        <v>1.191666666666666</v>
+        <v>1.529166666666666</v>
       </c>
     </row>
     <row r="122">
@@ -15526,7 +15526,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -15537,19 +15537,19 @@
         <v>48</v>
       </c>
       <c r="G134" t="n">
-        <v>4.313725490196078</v>
+        <v>4.590686274509804</v>
       </c>
       <c r="H134" t="n">
-        <v>0.5485127882985866</v>
+        <v>0.2861134470137242</v>
       </c>
       <c r="I134" t="n">
-        <v>0.07917100149453531</v>
+        <v>0.04129691891303634</v>
       </c>
       <c r="J134" t="n">
         <v>3.026960784313725</v>
       </c>
       <c r="K134" t="n">
-        <v>1.286764705882353</v>
+        <v>1.563725490196079</v>
       </c>
     </row>
     <row r="135">
@@ -15569,7 +15569,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -15580,19 +15580,19 @@
         <v>48</v>
       </c>
       <c r="G135" t="n">
-        <v>4.202205882352941</v>
+        <v>4.549019607843137</v>
       </c>
       <c r="H135" t="n">
-        <v>0.695258629277144</v>
+        <v>0.5468997754630919</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1003519391923923</v>
+        <v>0.0789381831458405</v>
       </c>
       <c r="J135" t="n">
         <v>3.004901960784314</v>
       </c>
       <c r="K135" t="n">
-        <v>1.197303921568627</v>
+        <v>1.544117647058823</v>
       </c>
     </row>
     <row r="136">
@@ -15612,7 +15612,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -15623,19 +15623,19 @@
         <v>48</v>
       </c>
       <c r="G136" t="n">
-        <v>4.313725490196078</v>
+        <v>4.590686274509804</v>
       </c>
       <c r="H136" t="n">
-        <v>0.5485127882985866</v>
+        <v>0.2861134470137242</v>
       </c>
       <c r="I136" t="n">
-        <v>0.07917100149453531</v>
+        <v>0.04129691891303634</v>
       </c>
       <c r="J136" t="n">
         <v>3.026960784313725</v>
       </c>
       <c r="K136" t="n">
-        <v>1.286764705882353</v>
+        <v>1.563725490196079</v>
       </c>
     </row>
     <row r="137">
@@ -15655,7 +15655,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -15666,19 +15666,19 @@
         <v>48</v>
       </c>
       <c r="G137" t="n">
-        <v>4.202205882352941</v>
+        <v>4.549019607843137</v>
       </c>
       <c r="H137" t="n">
-        <v>0.695258629277144</v>
+        <v>0.5468997754630919</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1003519391923923</v>
+        <v>0.0789381831458405</v>
       </c>
       <c r="J137" t="n">
         <v>3.004901960784314</v>
       </c>
       <c r="K137" t="n">
-        <v>1.197303921568627</v>
+        <v>1.544117647058823</v>
       </c>
     </row>
     <row r="138">
